--- a/src/main/resources/documents/2026/prijedlozi BO/03553..xlsx
+++ b/src/main/resources/documents/2026/prijedlozi BO/03553..xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10810"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Korisnik\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vladanmalinic/Documents/GitHub/flow-crm-tutorial/src/main/resources/documents/2026/prijedlozi BO/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{893D5867-D7C1-A04B-9F86-76CDE6FEB0C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15360" windowHeight="8208"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="БО-ТАБЕЛА" sheetId="1" r:id="rId1"/>
@@ -483,9 +484,6 @@
     <t>РАИФАЈСЕН БАНКА</t>
   </si>
   <si>
-    <t>КРНДИЈА ВЛАЈКО</t>
-  </si>
-  <si>
     <t>1708973192678</t>
   </si>
   <si>
@@ -550,9 +548,6 @@
   </si>
   <si>
     <t>5551000060323686</t>
-  </si>
-  <si>
-    <t>МАРИЋ ЊЕГОШ</t>
   </si>
   <si>
     <t>ССС ТЕХН.ЕЛЕКТРНИКЕ</t>
@@ -1775,9 +1770,6 @@
     <t>5551000053344633</t>
   </si>
   <si>
-    <t>ДРАГОЈЕВИЋ ИВА</t>
-  </si>
-  <si>
     <t>ССС ВЕТЕРИНАРСКИ ТЕНИЧАР</t>
   </si>
   <si>
@@ -2190,12 +2182,21 @@
   </si>
   <si>
     <t>2812975193049</t>
+  </si>
+  <si>
+    <t>ВЛАЈКО КРНДИЈА</t>
+  </si>
+  <si>
+    <t>ЊЕГОШ МАРИЋ</t>
+  </si>
+  <si>
+    <t>ИВА ДРАГОЈЕВИЋ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2405,7 +2406,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2426,9 +2427,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2469,22 +2467,19 @@
     <xf numFmtId="49" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2764,14 +2759,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L325"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="60" customWidth="1"/>
-    <col min="5" max="5" width="20" style="16" customWidth="1"/>
+    <col min="5" max="5" width="20" style="15" customWidth="1"/>
     <col min="6" max="6" width="8" customWidth="1"/>
     <col min="7" max="8" width="25" customWidth="1"/>
     <col min="9" max="9" width="35" customWidth="1"/>
@@ -2779,7 +2774,7 @@
     <col min="11" max="12" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2792,7 +2787,7 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="16" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -2815,7 +2810,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
@@ -2835,14 +2830,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="13"/>
+      <c r="E3" s="12"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
@@ -2851,43 +2846,43 @@
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B4" s="5"/>
       <c r="D4" t="s">
+        <v>289</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>290</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G4" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="H4" s="11" t="s">
         <v>292</v>
       </c>
-      <c r="F4" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="G4" s="12" t="s">
+      <c r="I4" s="11" t="s">
         <v>293</v>
       </c>
-      <c r="H4" s="12" t="s">
-        <v>294</v>
-      </c>
-      <c r="I4" s="12" t="s">
-        <v>295</v>
-      </c>
-      <c r="J4" s="18" t="s">
+      <c r="J4" s="17" t="s">
         <v>153</v>
       </c>
       <c r="K4" s="5"/>
       <c r="L4" s="5"/>
     </row>
-    <row r="5" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="13"/>
+      <c r="E5" s="12"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
@@ -2896,36 +2891,36 @@
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
     </row>
-    <row r="6" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B6" s="5"/>
-      <c r="D6" s="24" t="s">
-        <v>612</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>613</v>
+      <c r="D6" s="22" t="s">
+        <v>609</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>610</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>149</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
     </row>
-    <row r="7" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>17</v>
       </c>
@@ -2945,14 +2940,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="13"/>
+      <c r="E8" s="12"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
@@ -2961,43 +2956,43 @@
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
     </row>
-    <row r="9" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B9" s="5"/>
       <c r="D9" t="s">
-        <v>594</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>595</v>
+        <v>591</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>592</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>145</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="K9" s="5"/>
       <c r="L9" s="5"/>
     </row>
-    <row r="10" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="13"/>
+      <c r="E10" s="12"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
@@ -3006,36 +3001,36 @@
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
     </row>
-    <row r="11" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B11" s="5"/>
       <c r="D11" t="s">
-        <v>599</v>
-      </c>
-      <c r="E11" s="14" t="s">
-        <v>411</v>
+        <v>596</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>409</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>145</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="K11" s="5"/>
       <c r="L11" s="5"/>
     </row>
-    <row r="12" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>19</v>
       </c>
@@ -3055,14 +3050,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E13" s="13"/>
+      <c r="E13" s="12"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
@@ -3071,43 +3066,43 @@
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
     </row>
-    <row r="14" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B14" s="5"/>
       <c r="D14" t="s">
-        <v>251</v>
-      </c>
-      <c r="E14" s="14" t="s">
-        <v>252</v>
+        <v>249</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>250</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>149</v>
       </c>
       <c r="G14" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="I14" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="H14" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>256</v>
-      </c>
       <c r="J14" s="6" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="K14" s="5"/>
       <c r="L14" s="5"/>
     </row>
-    <row r="15" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E15" s="13"/>
+      <c r="E15" s="12"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
@@ -3116,36 +3111,36 @@
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
     </row>
-    <row r="16" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B16" s="5"/>
       <c r="D16" t="s">
+        <v>480</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G16" s="11" t="s">
         <v>482</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="H16" s="11" t="s">
         <v>483</v>
       </c>
-      <c r="F16" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="G16" s="12" t="s">
+      <c r="I16" s="11" t="s">
         <v>484</v>
       </c>
-      <c r="H16" s="12" t="s">
-        <v>485</v>
-      </c>
-      <c r="I16" s="12" t="s">
-        <v>486</v>
-      </c>
-      <c r="J16" s="18" t="s">
-        <v>198</v>
+      <c r="J16" s="17" t="s">
+        <v>196</v>
       </c>
       <c r="K16" s="5"/>
       <c r="L16" s="5"/>
     </row>
-    <row r="17" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>21</v>
       </c>
@@ -3165,14 +3160,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E18" s="13"/>
+      <c r="E18" s="12"/>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
@@ -3181,43 +3176,43 @@
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
     </row>
-    <row r="19" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B19" s="5"/>
       <c r="D19" t="s">
+        <v>269</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>270</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="G19" s="11" t="s">
         <v>271</v>
       </c>
-      <c r="E19" s="14" t="s">
+      <c r="H19" s="11" t="s">
         <v>272</v>
       </c>
-      <c r="F19" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="G19" s="12" t="s">
+      <c r="I19" s="11" t="s">
         <v>273</v>
       </c>
-      <c r="H19" s="12" t="s">
-        <v>274</v>
-      </c>
-      <c r="I19" s="12" t="s">
-        <v>275</v>
-      </c>
-      <c r="J19" s="18" t="s">
-        <v>163</v>
+      <c r="J19" s="17" t="s">
+        <v>162</v>
       </c>
       <c r="K19" s="5"/>
       <c r="L19" s="5"/>
     </row>
-    <row r="20" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E20" s="13"/>
+      <c r="E20" s="12"/>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
@@ -3226,36 +3221,36 @@
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
     </row>
-    <row r="21" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B21" s="5"/>
       <c r="D21" t="s">
+        <v>562</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G21" s="11" t="s">
+        <v>563</v>
+      </c>
+      <c r="H21" s="11" t="s">
         <v>564</v>
       </c>
-      <c r="E21" s="14" t="s">
-        <v>287</v>
-      </c>
-      <c r="F21" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="G21" s="12" t="s">
+      <c r="I21" s="11" t="s">
         <v>565</v>
       </c>
-      <c r="H21" s="12" t="s">
-        <v>566</v>
-      </c>
-      <c r="I21" s="12" t="s">
-        <v>567</v>
-      </c>
-      <c r="J21" s="18" t="s">
-        <v>198</v>
+      <c r="J21" s="17" t="s">
+        <v>196</v>
       </c>
       <c r="K21" s="5"/>
       <c r="L21" s="5"/>
     </row>
-    <row r="22" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>23</v>
       </c>
@@ -3275,14 +3270,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E23" s="13"/>
+      <c r="E23" s="12"/>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
@@ -3291,43 +3286,43 @@
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
     </row>
-    <row r="24" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B24" s="5"/>
       <c r="D24" t="s">
+        <v>284</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G24" s="11" t="s">
         <v>286</v>
       </c>
-      <c r="E24" s="14" t="s">
+      <c r="H24" s="11" t="s">
         <v>287</v>
       </c>
-      <c r="F24" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="G24" s="12" t="s">
+      <c r="I24" s="11" t="s">
         <v>288</v>
       </c>
-      <c r="H24" s="12" t="s">
-        <v>289</v>
-      </c>
-      <c r="I24" s="12" t="s">
-        <v>290</v>
-      </c>
-      <c r="J24" s="18" t="s">
-        <v>187</v>
+      <c r="J24" s="17" t="s">
+        <v>185</v>
       </c>
       <c r="K24" s="5"/>
       <c r="L24" s="5"/>
     </row>
-    <row r="25" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
       <c r="D25" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E25" s="13"/>
+      <c r="E25" s="12"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
@@ -3336,36 +3331,36 @@
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
     </row>
-    <row r="26" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B26" s="5"/>
       <c r="D26" t="s">
-        <v>706</v>
-      </c>
-      <c r="E26" s="14" t="s">
-        <v>707</v>
+        <v>703</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>704</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>149</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="K26" s="5"/>
       <c r="L26" s="5"/>
     </row>
-    <row r="27" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>25</v>
       </c>
@@ -3385,14 +3380,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
       <c r="D28" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E28" s="13"/>
+      <c r="E28" s="12"/>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
@@ -3401,43 +3396,43 @@
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
     </row>
-    <row r="29" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B29" s="5"/>
       <c r="D29" t="s">
+        <v>413</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>414</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="G29" s="11" t="s">
         <v>415</v>
       </c>
-      <c r="E29" s="14" t="s">
+      <c r="H29" s="11" t="s">
         <v>416</v>
       </c>
-      <c r="F29" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="G29" s="12" t="s">
+      <c r="I29" s="11" t="s">
         <v>417</v>
       </c>
-      <c r="H29" s="12" t="s">
+      <c r="J29" s="17" t="s">
         <v>418</v>
-      </c>
-      <c r="I29" s="12" t="s">
-        <v>419</v>
-      </c>
-      <c r="J29" s="18" t="s">
-        <v>420</v>
       </c>
       <c r="K29" s="5"/>
       <c r="L29" s="5"/>
     </row>
-    <row r="30" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E30" s="13"/>
+      <c r="E30" s="12"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
@@ -3446,36 +3441,36 @@
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
     </row>
-    <row r="31" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B31" s="5"/>
       <c r="D31" t="s">
+        <v>419</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>345</v>
+      </c>
+      <c r="F31" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="G31" s="11" t="s">
+        <v>420</v>
+      </c>
+      <c r="H31" s="11" t="s">
         <v>421</v>
       </c>
-      <c r="E31" s="14" t="s">
-        <v>347</v>
-      </c>
-      <c r="F31" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="G31" s="12" t="s">
+      <c r="I31" s="11" t="s">
         <v>422</v>
       </c>
-      <c r="H31" s="12" t="s">
-        <v>423</v>
-      </c>
-      <c r="I31" s="12" t="s">
-        <v>424</v>
-      </c>
-      <c r="J31" s="18" t="s">
-        <v>187</v>
+      <c r="J31" s="17" t="s">
+        <v>185</v>
       </c>
       <c r="K31" s="5"/>
       <c r="L31" s="5"/>
     </row>
-    <row r="32" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>27</v>
       </c>
@@ -3495,14 +3490,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
       <c r="D33" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E33" s="13"/>
+      <c r="E33" s="12"/>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
@@ -3511,43 +3506,43 @@
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
     </row>
-    <row r="34" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B34" s="5"/>
       <c r="D34" t="s">
+        <v>158</v>
+      </c>
+      <c r="E34" s="13" t="s">
         <v>159</v>
-      </c>
-      <c r="E34" s="14" t="s">
-        <v>160</v>
       </c>
       <c r="F34" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="G34" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H34" s="8" t="s">
+      <c r="G34" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="H34" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="I34" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="I34" s="7" t="s">
+      <c r="J34" s="6" t="s">
         <v>162</v>
-      </c>
-      <c r="J34" s="6" t="s">
-        <v>163</v>
       </c>
       <c r="K34" s="5"/>
       <c r="L34" s="5"/>
     </row>
-    <row r="35" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
       <c r="D35" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E35" s="13"/>
+      <c r="E35" s="12"/>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
@@ -3556,36 +3551,36 @@
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
     </row>
-    <row r="36" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B36" s="5"/>
       <c r="D36" t="s">
+        <v>325</v>
+      </c>
+      <c r="E36" s="13" t="s">
+        <v>326</v>
+      </c>
+      <c r="F36" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="G36" s="11" t="s">
         <v>327</v>
       </c>
-      <c r="E36" s="14" t="s">
+      <c r="H36" s="11" t="s">
         <v>328</v>
       </c>
-      <c r="F36" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="G36" s="12" t="s">
+      <c r="I36" s="11" t="s">
         <v>329</v>
       </c>
-      <c r="H36" s="12" t="s">
-        <v>330</v>
-      </c>
-      <c r="I36" s="12" t="s">
-        <v>331</v>
-      </c>
-      <c r="J36" s="18" t="s">
-        <v>198</v>
+      <c r="J36" s="17" t="s">
+        <v>196</v>
       </c>
       <c r="K36" s="5"/>
       <c r="L36" s="5"/>
     </row>
-    <row r="37" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>29</v>
       </c>
@@ -3605,14 +3600,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
       <c r="D38" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E38" s="13"/>
+      <c r="E38" s="12"/>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
@@ -3621,43 +3616,43 @@
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
     </row>
-    <row r="39" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B39" s="5"/>
       <c r="D39" t="s">
+        <v>465</v>
+      </c>
+      <c r="E39" s="13" t="s">
+        <v>466</v>
+      </c>
+      <c r="F39" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="G39" s="11" t="s">
         <v>467</v>
       </c>
-      <c r="E39" s="14" t="s">
+      <c r="H39" s="11" t="s">
         <v>468</v>
       </c>
-      <c r="F39" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="G39" s="12" t="s">
+      <c r="I39" s="11" t="s">
         <v>469</v>
       </c>
-      <c r="H39" s="12" t="s">
-        <v>470</v>
-      </c>
-      <c r="I39" s="12" t="s">
-        <v>471</v>
-      </c>
-      <c r="J39" s="18" t="s">
-        <v>163</v>
+      <c r="J39" s="17" t="s">
+        <v>162</v>
       </c>
       <c r="K39" s="5"/>
       <c r="L39" s="5"/>
     </row>
-    <row r="40" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
       <c r="D40" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E40" s="13"/>
+      <c r="E40" s="12"/>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
@@ -3666,28 +3661,28 @@
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
     </row>
-    <row r="41" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B41" s="5"/>
       <c r="D41" t="s">
-        <v>714</v>
-      </c>
-      <c r="E41" s="14" t="s">
-        <v>669</v>
+        <v>711</v>
+      </c>
+      <c r="E41" s="13" t="s">
+        <v>666</v>
       </c>
       <c r="F41" s="7" t="s">
         <v>145</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="I41" s="7" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="J41" s="6" t="s">
         <v>153</v>
@@ -3695,7 +3690,7 @@
       <c r="K41" s="5"/>
       <c r="L41" s="5"/>
     </row>
-    <row r="42" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>31</v>
       </c>
@@ -3715,14 +3710,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
       <c r="D43" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E43" s="13"/>
+      <c r="E43" s="12"/>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
@@ -3731,43 +3726,43 @@
       <c r="K43" s="1"/>
       <c r="L43" s="1"/>
     </row>
-    <row r="44" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" ht="24" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B44" s="5"/>
       <c r="D44" t="s">
+        <v>485</v>
+      </c>
+      <c r="E44" s="20" t="s">
+        <v>486</v>
+      </c>
+      <c r="F44" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="G44" s="11" t="s">
         <v>487</v>
       </c>
-      <c r="E44" s="21" t="s">
+      <c r="H44" s="11" t="s">
         <v>488</v>
       </c>
-      <c r="F44" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="G44" s="12" t="s">
+      <c r="I44" s="11" t="s">
         <v>489</v>
       </c>
-      <c r="H44" s="12" t="s">
-        <v>490</v>
-      </c>
-      <c r="I44" s="12" t="s">
-        <v>491</v>
-      </c>
-      <c r="J44" s="18" t="s">
-        <v>187</v>
+      <c r="J44" s="17" t="s">
+        <v>185</v>
       </c>
       <c r="K44" s="5"/>
       <c r="L44" s="5"/>
     </row>
-    <row r="45" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
       <c r="D45" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E45" s="13"/>
+      <c r="E45" s="12"/>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
@@ -3776,12 +3771,12 @@
       <c r="K45" s="1"/>
       <c r="L45" s="1"/>
     </row>
-    <row r="46" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B46" s="5"/>
-      <c r="E46" s="14"/>
+      <c r="E46" s="13"/>
       <c r="F46" s="5"/>
       <c r="G46" s="5"/>
       <c r="H46" s="5"/>
@@ -3790,7 +3785,7 @@
       <c r="K46" s="5"/>
       <c r="L46" s="5"/>
     </row>
-    <row r="47" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
         <v>33</v>
       </c>
@@ -3810,14 +3805,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
       <c r="D48" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E48" s="13"/>
+      <c r="E48" s="12"/>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
@@ -3826,43 +3821,43 @@
       <c r="K48" s="1"/>
       <c r="L48" s="1"/>
     </row>
-    <row r="49" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B49" s="5"/>
       <c r="D49" t="s">
-        <v>634</v>
-      </c>
-      <c r="E49" s="14" t="s">
-        <v>635</v>
+        <v>631</v>
+      </c>
+      <c r="E49" s="13" t="s">
+        <v>632</v>
       </c>
       <c r="F49" s="7" t="s">
         <v>145</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="I49" s="7" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="K49" s="5"/>
       <c r="L49" s="5"/>
     </row>
-    <row r="50" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
       <c r="D50" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E50" s="13"/>
+      <c r="E50" s="12"/>
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
@@ -3871,12 +3866,12 @@
       <c r="K50" s="1"/>
       <c r="L50" s="1"/>
     </row>
-    <row r="51" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B51" s="5"/>
-      <c r="E51" s="14"/>
+      <c r="E51" s="13"/>
       <c r="F51" s="5"/>
       <c r="G51" s="5"/>
       <c r="H51" s="5"/>
@@ -3885,7 +3880,7 @@
       <c r="K51" s="5"/>
       <c r="L51" s="5"/>
     </row>
-    <row r="52" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
         <v>35</v>
       </c>
@@ -3905,14 +3900,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="53" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
       <c r="D53" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E53" s="13"/>
+      <c r="E53" s="12"/>
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
       <c r="H53" s="1"/>
@@ -3921,43 +3916,43 @@
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
     </row>
-    <row r="54" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B54" s="5"/>
       <c r="D54" t="s">
+        <v>304</v>
+      </c>
+      <c r="E54" s="13" t="s">
+        <v>305</v>
+      </c>
+      <c r="F54" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G54" s="11" t="s">
         <v>306</v>
       </c>
-      <c r="E54" s="14" t="s">
+      <c r="H54" s="11" t="s">
         <v>307</v>
       </c>
-      <c r="F54" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="G54" s="12" t="s">
+      <c r="I54" s="11" t="s">
         <v>308</v>
       </c>
-      <c r="H54" s="12" t="s">
+      <c r="J54" s="17" t="s">
         <v>309</v>
-      </c>
-      <c r="I54" s="12" t="s">
-        <v>310</v>
-      </c>
-      <c r="J54" s="18" t="s">
-        <v>311</v>
       </c>
       <c r="K54" s="5"/>
       <c r="L54" s="5"/>
     </row>
-    <row r="55" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
       <c r="D55" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E55" s="13"/>
+      <c r="E55" s="12"/>
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
       <c r="H55" s="1"/>
@@ -3966,36 +3961,36 @@
       <c r="K55" s="1"/>
       <c r="L55" s="1"/>
     </row>
-    <row r="56" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A56" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B56" s="5"/>
       <c r="D56" t="s">
+        <v>436</v>
+      </c>
+      <c r="E56" s="13" t="s">
+        <v>381</v>
+      </c>
+      <c r="F56" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G56" s="11" t="s">
+        <v>437</v>
+      </c>
+      <c r="H56" s="11" t="s">
         <v>438</v>
       </c>
-      <c r="E56" s="14" t="s">
-        <v>383</v>
-      </c>
-      <c r="F56" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="G56" s="12" t="s">
+      <c r="I56" s="11" t="s">
         <v>439</v>
       </c>
-      <c r="H56" s="12" t="s">
-        <v>440</v>
-      </c>
-      <c r="I56" s="12" t="s">
-        <v>441</v>
-      </c>
-      <c r="J56" s="18" t="s">
-        <v>311</v>
+      <c r="J56" s="17" t="s">
+        <v>309</v>
       </c>
       <c r="K56" s="5"/>
       <c r="L56" s="5"/>
     </row>
-    <row r="57" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
         <v>37</v>
       </c>
@@ -4015,14 +4010,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="58" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
       <c r="D58" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E58" s="13"/>
+      <c r="E58" s="12"/>
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
       <c r="H58" s="1"/>
@@ -4031,43 +4026,43 @@
       <c r="K58" s="1"/>
       <c r="L58" s="1"/>
     </row>
-    <row r="59" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B59" s="5"/>
       <c r="D59" t="s">
-        <v>644</v>
-      </c>
-      <c r="E59" s="14" t="s">
-        <v>645</v>
+        <v>641</v>
+      </c>
+      <c r="E59" s="13" t="s">
+        <v>642</v>
       </c>
       <c r="F59" s="7" t="s">
         <v>149</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="H59" s="7" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="I59" s="7" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="J59" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="K59" s="5"/>
       <c r="L59" s="5"/>
     </row>
-    <row r="60" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
       <c r="D60" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E60" s="13"/>
+      <c r="E60" s="12"/>
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
       <c r="H60" s="1"/>
@@ -4076,28 +4071,28 @@
       <c r="K60" s="1"/>
       <c r="L60" s="1"/>
     </row>
-    <row r="61" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A61" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B61" s="5"/>
       <c r="D61" t="s">
-        <v>673</v>
-      </c>
-      <c r="E61" s="14" t="s">
-        <v>674</v>
+        <v>670</v>
+      </c>
+      <c r="E61" s="13" t="s">
+        <v>671</v>
       </c>
       <c r="F61" s="7" t="s">
         <v>145</v>
       </c>
       <c r="G61" s="7" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="H61" s="7" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="I61" s="7" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="J61" s="6" t="s">
         <v>153</v>
@@ -4105,7 +4100,7 @@
       <c r="K61" s="5"/>
       <c r="L61" s="5"/>
     </row>
-    <row r="62" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
         <v>39</v>
       </c>
@@ -4125,14 +4120,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="63" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
       <c r="D63" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E63" s="13"/>
+      <c r="E63" s="12"/>
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
       <c r="H63" s="1"/>
@@ -4141,43 +4136,43 @@
       <c r="K63" s="1"/>
       <c r="L63" s="1"/>
     </row>
-    <row r="64" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A64" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B64" s="5"/>
       <c r="D64" t="s">
-        <v>154</v>
-      </c>
-      <c r="E64" s="14" t="s">
-        <v>164</v>
+        <v>719</v>
+      </c>
+      <c r="E64" s="13" t="s">
+        <v>163</v>
       </c>
       <c r="F64" s="7" t="s">
         <v>145</v>
       </c>
       <c r="G64" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="H64" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="H64" s="7" t="s">
+      <c r="I64" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="I64" s="7" t="s">
+      <c r="J64" s="6" t="s">
         <v>157</v>
-      </c>
-      <c r="J64" s="6" t="s">
-        <v>158</v>
       </c>
       <c r="K64" s="5"/>
       <c r="L64" s="5"/>
     </row>
-    <row r="65" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
       <c r="D65" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E65" s="13"/>
+      <c r="E65" s="12"/>
       <c r="F65" s="1"/>
       <c r="G65" s="1"/>
       <c r="H65" s="1"/>
@@ -4186,36 +4181,36 @@
       <c r="K65" s="1"/>
       <c r="L65" s="1"/>
     </row>
-    <row r="66" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A66" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B66" s="5"/>
       <c r="D66" t="s">
+        <v>427</v>
+      </c>
+      <c r="E66" s="13" t="s">
+        <v>364</v>
+      </c>
+      <c r="F66" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G66" s="11" t="s">
+        <v>428</v>
+      </c>
+      <c r="H66" s="11" t="s">
         <v>429</v>
       </c>
-      <c r="E66" s="14" t="s">
-        <v>366</v>
-      </c>
-      <c r="F66" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="G66" s="12" t="s">
+      <c r="I66" s="11" t="s">
         <v>430</v>
       </c>
-      <c r="H66" s="12" t="s">
-        <v>431</v>
-      </c>
-      <c r="I66" s="12" t="s">
-        <v>432</v>
-      </c>
-      <c r="J66" s="18" t="s">
-        <v>163</v>
+      <c r="J66" s="17" t="s">
+        <v>162</v>
       </c>
       <c r="K66" s="5"/>
       <c r="L66" s="5"/>
     </row>
-    <row r="67" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
         <v>41</v>
       </c>
@@ -4235,14 +4230,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="68" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
       <c r="D68" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E68" s="13"/>
+      <c r="E68" s="12"/>
       <c r="F68" s="1"/>
       <c r="G68" s="1"/>
       <c r="H68" s="1"/>
@@ -4251,43 +4246,43 @@
       <c r="K68" s="1"/>
       <c r="L68" s="1"/>
     </row>
-    <row r="69" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A69" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B69" s="5"/>
       <c r="D69" t="s">
-        <v>177</v>
-      </c>
-      <c r="E69" s="14" t="s">
-        <v>178</v>
+        <v>720</v>
+      </c>
+      <c r="E69" s="13" t="s">
+        <v>176</v>
       </c>
       <c r="F69" s="7" t="s">
         <v>145</v>
       </c>
       <c r="G69" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="H69" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="I69" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="H69" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="I69" s="7" t="s">
-        <v>181</v>
-      </c>
       <c r="J69" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K69" s="5"/>
       <c r="L69" s="5"/>
     </row>
-    <row r="70" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
       <c r="D70" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E70" s="13"/>
+      <c r="E70" s="12"/>
       <c r="F70" s="1"/>
       <c r="G70" s="1"/>
       <c r="H70" s="1"/>
@@ -4296,36 +4291,36 @@
       <c r="K70" s="1"/>
       <c r="L70" s="1"/>
     </row>
-    <row r="71" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A71" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B71" s="5"/>
       <c r="D71" t="s">
-        <v>639</v>
-      </c>
-      <c r="E71" s="14" t="s">
-        <v>640</v>
+        <v>636</v>
+      </c>
+      <c r="E71" s="13" t="s">
+        <v>637</v>
       </c>
       <c r="F71" s="7" t="s">
         <v>149</v>
       </c>
       <c r="G71" s="7" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="H71" s="7" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="I71" s="7" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="J71" s="6" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="K71" s="5"/>
       <c r="L71" s="5"/>
     </row>
-    <row r="72" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
         <v>43</v>
       </c>
@@ -4345,14 +4340,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="73" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
       <c r="D73" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E73" s="13"/>
+      <c r="E73" s="12"/>
       <c r="F73" s="1"/>
       <c r="G73" s="1"/>
       <c r="H73" s="1"/>
@@ -4361,43 +4356,43 @@
       <c r="K73" s="1"/>
       <c r="L73" s="1"/>
     </row>
-    <row r="74" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A74" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B74" s="5"/>
       <c r="D74" t="s">
-        <v>225</v>
-      </c>
-      <c r="E74" s="14" t="s">
-        <v>226</v>
+        <v>223</v>
+      </c>
+      <c r="E74" s="13" t="s">
+        <v>224</v>
       </c>
       <c r="F74" s="7" t="s">
         <v>149</v>
       </c>
       <c r="G74" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="H74" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="I74" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="H74" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="I74" s="7" t="s">
-        <v>229</v>
-      </c>
       <c r="J74" s="6" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="K74" s="5"/>
       <c r="L74" s="5"/>
     </row>
-    <row r="75" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
       <c r="D75" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E75" s="13"/>
+      <c r="E75" s="12"/>
       <c r="F75" s="1"/>
       <c r="G75" s="1"/>
       <c r="H75" s="1"/>
@@ -4406,12 +4401,12 @@
       <c r="K75" s="1"/>
       <c r="L75" s="1"/>
     </row>
-    <row r="76" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A76" s="7" t="s">
         <v>15</v>
       </c>
       <c r="B76" s="5"/>
-      <c r="E76" s="14"/>
+      <c r="E76" s="13"/>
       <c r="F76" s="5"/>
       <c r="G76" s="5"/>
       <c r="H76" s="5"/>
@@ -4420,7 +4415,7 @@
       <c r="K76" s="5"/>
       <c r="L76" s="5"/>
     </row>
-    <row r="77" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
         <v>45</v>
       </c>
@@ -4440,14 +4435,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="78" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
       <c r="D78" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E78" s="13"/>
+      <c r="E78" s="12"/>
       <c r="F78" s="1"/>
       <c r="G78" s="1"/>
       <c r="H78" s="1"/>
@@ -4456,28 +4451,28 @@
       <c r="K78" s="1"/>
       <c r="L78" s="1"/>
     </row>
-    <row r="79" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B79" s="5"/>
       <c r="D79" t="s">
+        <v>167</v>
+      </c>
+      <c r="E79" s="13" t="s">
         <v>168</v>
-      </c>
-      <c r="E79" s="14" t="s">
-        <v>169</v>
       </c>
       <c r="F79" s="7" t="s">
         <v>149</v>
       </c>
       <c r="G79" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="H79" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="H79" s="7" t="s">
+      <c r="I79" s="7" t="s">
         <v>171</v>
-      </c>
-      <c r="I79" s="7" t="s">
-        <v>172</v>
       </c>
       <c r="J79" s="6" t="s">
         <v>153</v>
@@ -4485,14 +4480,14 @@
       <c r="K79" s="5"/>
       <c r="L79" s="5"/>
     </row>
-    <row r="80" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
       <c r="D80" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E80" s="13"/>
+      <c r="E80" s="12"/>
       <c r="F80" s="1"/>
       <c r="G80" s="1"/>
       <c r="H80" s="1"/>
@@ -4501,36 +4496,36 @@
       <c r="K80" s="1"/>
       <c r="L80" s="1"/>
     </row>
-    <row r="81" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A81" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B81" s="5"/>
       <c r="D81" t="s">
+        <v>423</v>
+      </c>
+      <c r="E81" s="13" t="s">
+        <v>345</v>
+      </c>
+      <c r="F81" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G81" s="11" t="s">
+        <v>424</v>
+      </c>
+      <c r="H81" s="11" t="s">
         <v>425</v>
       </c>
-      <c r="E81" s="14" t="s">
-        <v>347</v>
-      </c>
-      <c r="F81" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="G81" s="12" t="s">
+      <c r="I81" s="11" t="s">
         <v>426</v>
       </c>
-      <c r="H81" s="12" t="s">
-        <v>427</v>
-      </c>
-      <c r="I81" s="12" t="s">
-        <v>428</v>
-      </c>
-      <c r="J81" s="18" t="s">
-        <v>163</v>
+      <c r="J81" s="17" t="s">
+        <v>162</v>
       </c>
       <c r="K81" s="5"/>
       <c r="L81" s="5"/>
     </row>
-    <row r="82" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
         <v>47</v>
       </c>
@@ -4550,14 +4545,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="83" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
       <c r="D83" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E83" s="13"/>
+      <c r="E83" s="12"/>
       <c r="F83" s="1"/>
       <c r="G83" s="1"/>
       <c r="H83" s="1"/>
@@ -4566,43 +4561,43 @@
       <c r="K83" s="1"/>
       <c r="L83" s="1"/>
     </row>
-    <row r="84" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A84" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B84" s="5"/>
       <c r="D84" t="s">
+        <v>339</v>
+      </c>
+      <c r="E84" s="13" t="s">
+        <v>340</v>
+      </c>
+      <c r="F84" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="G84" s="11" t="s">
         <v>341</v>
       </c>
-      <c r="E84" s="14" t="s">
+      <c r="H84" s="11" t="s">
         <v>342</v>
       </c>
-      <c r="F84" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="G84" s="12" t="s">
+      <c r="I84" s="11" t="s">
         <v>343</v>
       </c>
-      <c r="H84" s="12" t="s">
-        <v>344</v>
-      </c>
-      <c r="I84" s="12" t="s">
-        <v>345</v>
-      </c>
-      <c r="J84" s="18" t="s">
+      <c r="J84" s="17" t="s">
         <v>153</v>
       </c>
       <c r="K84" s="5"/>
       <c r="L84" s="5"/>
     </row>
-    <row r="85" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
       <c r="D85" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E85" s="13"/>
+      <c r="E85" s="12"/>
       <c r="F85" s="1"/>
       <c r="G85" s="1"/>
       <c r="H85" s="1"/>
@@ -4611,36 +4606,36 @@
       <c r="K85" s="1"/>
       <c r="L85" s="1"/>
     </row>
-    <row r="86" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A86" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B86" s="5"/>
       <c r="D86" t="s">
-        <v>603</v>
-      </c>
-      <c r="E86" s="14" t="s">
-        <v>383</v>
+        <v>600</v>
+      </c>
+      <c r="E86" s="13" t="s">
+        <v>381</v>
       </c>
       <c r="F86" s="7" t="s">
         <v>145</v>
       </c>
       <c r="G86" s="7" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="H86" s="7" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="I86" s="7" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="J86" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="K86" s="5"/>
       <c r="L86" s="5"/>
     </row>
-    <row r="87" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
         <v>49</v>
       </c>
@@ -4660,14 +4655,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="88" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
       <c r="D88" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E88" s="13"/>
+      <c r="E88" s="12"/>
       <c r="F88" s="1"/>
       <c r="G88" s="1"/>
       <c r="H88" s="1"/>
@@ -4676,43 +4671,43 @@
       <c r="K88" s="1"/>
       <c r="L88" s="1"/>
     </row>
-    <row r="89" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A89" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B89" s="5"/>
       <c r="D89" t="s">
-        <v>664</v>
-      </c>
-      <c r="E89" s="14" t="s">
-        <v>347</v>
+        <v>661</v>
+      </c>
+      <c r="E89" s="13" t="s">
+        <v>345</v>
       </c>
       <c r="F89" s="7" t="s">
         <v>145</v>
       </c>
       <c r="G89" s="7" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="H89" s="7" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="I89" s="7" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="J89" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K89" s="5"/>
       <c r="L89" s="5"/>
     </row>
-    <row r="90" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
       <c r="D90" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E90" s="13"/>
+      <c r="E90" s="12"/>
       <c r="F90" s="1"/>
       <c r="G90" s="1"/>
       <c r="H90" s="1"/>
@@ -4721,36 +4716,36 @@
       <c r="K90" s="1"/>
       <c r="L90" s="1"/>
     </row>
-    <row r="91" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A91" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B91" s="5"/>
       <c r="D91" t="s">
+        <v>502</v>
+      </c>
+      <c r="E91" s="13" t="s">
+        <v>340</v>
+      </c>
+      <c r="F91" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="G91" s="11" t="s">
+        <v>503</v>
+      </c>
+      <c r="H91" s="11" t="s">
         <v>504</v>
       </c>
-      <c r="E91" s="14" t="s">
-        <v>342</v>
-      </c>
-      <c r="F91" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="G91" s="12" t="s">
-        <v>505</v>
-      </c>
-      <c r="H91" s="12" t="s">
-        <v>506</v>
-      </c>
-      <c r="I91" s="8" t="s">
-        <v>593</v>
-      </c>
-      <c r="J91" s="23" t="s">
-        <v>198</v>
+      <c r="I91" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="J91" s="6" t="s">
+        <v>196</v>
       </c>
       <c r="K91" s="5"/>
       <c r="L91" s="5"/>
     </row>
-    <row r="92" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
         <v>51</v>
       </c>
@@ -4770,14 +4765,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="93" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
       <c r="D93" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E93" s="13"/>
+      <c r="E93" s="12"/>
       <c r="F93" s="1"/>
       <c r="G93" s="1"/>
       <c r="H93" s="1"/>
@@ -4786,16 +4781,16 @@
       <c r="K93" s="1"/>
       <c r="L93" s="1"/>
     </row>
-    <row r="94" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A94" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B94" s="5"/>
       <c r="D94" t="s">
+        <v>165</v>
+      </c>
+      <c r="E94" s="13" t="s">
         <v>166</v>
-      </c>
-      <c r="E94" s="14" t="s">
-        <v>167</v>
       </c>
       <c r="F94" s="7" t="s">
         <v>149</v>
@@ -4815,14 +4810,14 @@
       <c r="K94" s="5"/>
       <c r="L94" s="5"/>
     </row>
-    <row r="95" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
       <c r="D95" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E95" s="13"/>
+      <c r="E95" s="12"/>
       <c r="F95" s="1"/>
       <c r="G95" s="1"/>
       <c r="H95" s="1"/>
@@ -4831,36 +4826,36 @@
       <c r="K95" s="1"/>
       <c r="L95" s="1"/>
     </row>
-    <row r="96" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A96" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B96" s="5"/>
       <c r="D96" t="s">
+        <v>510</v>
+      </c>
+      <c r="E96" s="13" t="s">
+        <v>511</v>
+      </c>
+      <c r="F96" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="G96" s="11" t="s">
         <v>512</v>
       </c>
-      <c r="E96" s="14" t="s">
+      <c r="H96" s="11" t="s">
         <v>513</v>
       </c>
-      <c r="F96" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="G96" s="12" t="s">
+      <c r="I96" s="11" t="s">
         <v>514</v>
       </c>
-      <c r="H96" s="12" t="s">
-        <v>515</v>
-      </c>
-      <c r="I96" s="12" t="s">
-        <v>516</v>
-      </c>
-      <c r="J96" s="18" t="s">
-        <v>163</v>
+      <c r="J96" s="17" t="s">
+        <v>162</v>
       </c>
       <c r="K96" s="5"/>
       <c r="L96" s="5"/>
     </row>
-    <row r="97" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
         <v>53</v>
       </c>
@@ -4880,14 +4875,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="98" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
-      <c r="D98" s="17" t="s">
+      <c r="D98" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="E98" s="13"/>
+      <c r="E98" s="12"/>
       <c r="F98" s="1"/>
       <c r="G98" s="1"/>
       <c r="H98" s="1"/>
@@ -4896,43 +4891,43 @@
       <c r="K98" s="1"/>
       <c r="L98" s="1"/>
     </row>
-    <row r="99" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A99" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B99" s="5"/>
       <c r="D99" t="s">
+        <v>294</v>
+      </c>
+      <c r="E99" s="13" t="s">
+        <v>295</v>
+      </c>
+      <c r="F99" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G99" s="11" t="s">
         <v>296</v>
       </c>
-      <c r="E99" s="14" t="s">
+      <c r="H99" s="11" t="s">
         <v>297</v>
       </c>
-      <c r="F99" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="G99" s="12" t="s">
+      <c r="I99" s="11" t="s">
         <v>298</v>
       </c>
-      <c r="H99" s="12" t="s">
-        <v>299</v>
-      </c>
-      <c r="I99" s="12" t="s">
-        <v>300</v>
-      </c>
-      <c r="J99" s="18" t="s">
-        <v>198</v>
+      <c r="J99" s="17" t="s">
+        <v>196</v>
       </c>
       <c r="K99" s="5"/>
       <c r="L99" s="5"/>
     </row>
-    <row r="100" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
-      <c r="C100" s="10"/>
+      <c r="C100" s="9"/>
       <c r="D100" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E100" s="13"/>
+      <c r="E100" s="12"/>
       <c r="F100" s="1"/>
       <c r="G100" s="1"/>
       <c r="H100" s="1"/>
@@ -4941,42 +4936,42 @@
       <c r="K100" s="1"/>
       <c r="L100" s="1"/>
     </row>
-    <row r="101" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A101" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B101" s="9"/>
-      <c r="C101" s="11"/>
+      <c r="B101" s="8"/>
+      <c r="C101" s="10"/>
       <c r="D101" t="s">
+        <v>354</v>
+      </c>
+      <c r="E101" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="F101" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="G101" s="11" t="s">
         <v>356</v>
       </c>
-      <c r="E101" s="14" t="s">
+      <c r="H101" s="11" t="s">
         <v>357</v>
       </c>
-      <c r="F101" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="G101" s="12" t="s">
+      <c r="I101" s="11" t="s">
         <v>358</v>
       </c>
-      <c r="H101" s="12" t="s">
-        <v>359</v>
-      </c>
-      <c r="I101" s="12" t="s">
-        <v>360</v>
-      </c>
-      <c r="J101" s="18" t="s">
+      <c r="J101" s="17" t="s">
         <v>153</v>
       </c>
       <c r="K101" s="5"/>
       <c r="L101" s="5"/>
     </row>
-    <row r="102" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A102" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B102" s="2"/>
-      <c r="C102" s="20"/>
+      <c r="C102" s="19"/>
       <c r="D102" s="25" t="s">
         <v>56</v>
       </c>
@@ -4991,14 +4986,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="103" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
       <c r="D103" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E103" s="13"/>
+      <c r="E103" s="12"/>
       <c r="F103" s="1"/>
       <c r="G103" s="1"/>
       <c r="H103" s="1"/>
@@ -5007,43 +5002,43 @@
       <c r="K103" s="1"/>
       <c r="L103" s="1"/>
     </row>
-    <row r="104" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A104" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B104" s="5"/>
       <c r="D104" t="s">
-        <v>617</v>
-      </c>
-      <c r="E104" s="14" t="s">
-        <v>411</v>
+        <v>614</v>
+      </c>
+      <c r="E104" s="13" t="s">
+        <v>409</v>
       </c>
       <c r="F104" s="7" t="s">
         <v>145</v>
       </c>
       <c r="G104" s="7" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="H104" s="7" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="I104" s="7" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="J104" s="6" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="K104" s="5"/>
       <c r="L104" s="5"/>
     </row>
-    <row r="105" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
       <c r="D105" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E105" s="13"/>
+      <c r="E105" s="12"/>
       <c r="F105" s="1"/>
       <c r="G105" s="1"/>
       <c r="H105" s="1"/>
@@ -5052,12 +5047,12 @@
       <c r="K105" s="1"/>
       <c r="L105" s="1"/>
     </row>
-    <row r="106" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A106" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B106" s="5"/>
-      <c r="E106" s="14"/>
+      <c r="E106" s="13"/>
       <c r="F106" s="5"/>
       <c r="G106" s="5"/>
       <c r="H106" s="5"/>
@@ -5066,7 +5061,7 @@
       <c r="K106" s="5"/>
       <c r="L106" s="5"/>
     </row>
-    <row r="107" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A107" s="2" t="s">
         <v>57</v>
       </c>
@@ -5086,14 +5081,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="108" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
       <c r="D108" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E108" s="13"/>
+      <c r="E108" s="12"/>
       <c r="F108" s="1"/>
       <c r="G108" s="1"/>
       <c r="H108" s="1"/>
@@ -5102,43 +5097,43 @@
       <c r="K108" s="1"/>
       <c r="L108" s="1"/>
     </row>
-    <row r="109" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A109" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B109" s="5"/>
       <c r="D109" t="s">
-        <v>182</v>
-      </c>
-      <c r="E109" s="14" t="s">
-        <v>183</v>
+        <v>180</v>
+      </c>
+      <c r="E109" s="13" t="s">
+        <v>181</v>
       </c>
       <c r="F109" s="7" t="s">
         <v>149</v>
       </c>
       <c r="G109" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="H109" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="I109" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="H109" s="7" t="s">
+      <c r="J109" s="6" t="s">
         <v>185</v>
-      </c>
-      <c r="I109" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="J109" s="6" t="s">
-        <v>187</v>
       </c>
       <c r="K109" s="5"/>
       <c r="L109" s="5"/>
     </row>
-    <row r="110" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
       <c r="D110" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E110" s="13"/>
+      <c r="E110" s="12"/>
       <c r="F110" s="1"/>
       <c r="G110" s="1"/>
       <c r="H110" s="1"/>
@@ -5147,36 +5142,36 @@
       <c r="K110" s="1"/>
       <c r="L110" s="1"/>
     </row>
-    <row r="111" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A111" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B111" s="5"/>
       <c r="D111" t="s">
+        <v>566</v>
+      </c>
+      <c r="E111" s="13" t="s">
+        <v>381</v>
+      </c>
+      <c r="F111" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G111" s="11" t="s">
+        <v>567</v>
+      </c>
+      <c r="H111" s="11" t="s">
         <v>568</v>
       </c>
-      <c r="E111" s="14" t="s">
-        <v>383</v>
-      </c>
-      <c r="F111" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="G111" s="12" t="s">
+      <c r="I111" s="11" t="s">
         <v>569</v>
       </c>
-      <c r="H111" s="12" t="s">
+      <c r="J111" s="17" t="s">
         <v>570</v>
-      </c>
-      <c r="I111" s="12" t="s">
-        <v>571</v>
-      </c>
-      <c r="J111" s="18" t="s">
-        <v>572</v>
       </c>
       <c r="K111" s="5"/>
       <c r="L111" s="5"/>
     </row>
-    <row r="112" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A112" s="2" t="s">
         <v>59</v>
       </c>
@@ -5196,14 +5191,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="113" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
       <c r="D113" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E113" s="13"/>
+      <c r="E113" s="12"/>
       <c r="F113" s="1"/>
       <c r="G113" s="1"/>
       <c r="H113" s="1"/>
@@ -5212,43 +5207,43 @@
       <c r="K113" s="1"/>
       <c r="L113" s="1"/>
     </row>
-    <row r="114" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A114" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B114" s="5"/>
       <c r="D114" t="s">
-        <v>209</v>
-      </c>
-      <c r="E114" s="14" t="s">
-        <v>210</v>
+        <v>207</v>
+      </c>
+      <c r="E114" s="13" t="s">
+        <v>208</v>
       </c>
       <c r="F114" s="7" t="s">
         <v>149</v>
       </c>
       <c r="G114" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="H114" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="I114" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="H114" s="7" t="s">
+      <c r="J114" s="6" t="s">
         <v>212</v>
-      </c>
-      <c r="I114" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="J114" s="6" t="s">
-        <v>214</v>
       </c>
       <c r="K114" s="5"/>
       <c r="L114" s="5"/>
     </row>
-    <row r="115" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
       <c r="D115" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E115" s="13"/>
+      <c r="E115" s="12"/>
       <c r="F115" s="1"/>
       <c r="G115" s="1"/>
       <c r="H115" s="1"/>
@@ -5257,12 +5252,12 @@
       <c r="K115" s="1"/>
       <c r="L115" s="1"/>
     </row>
-    <row r="116" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A116" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B116" s="5"/>
-      <c r="E116" s="14"/>
+      <c r="E116" s="13"/>
       <c r="F116" s="5"/>
       <c r="G116" s="5"/>
       <c r="H116" s="5"/>
@@ -5271,7 +5266,7 @@
       <c r="K116" s="5"/>
       <c r="L116" s="5"/>
     </row>
-    <row r="117" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A117" s="2" t="s">
         <v>61</v>
       </c>
@@ -5291,14 +5286,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="118" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
       <c r="D118" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E118" s="13"/>
+      <c r="E118" s="12"/>
       <c r="F118" s="1"/>
       <c r="G118" s="1"/>
       <c r="H118" s="1"/>
@@ -5307,43 +5302,43 @@
       <c r="K118" s="1"/>
       <c r="L118" s="1"/>
     </row>
-    <row r="119" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A119" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B119" s="5"/>
       <c r="D119" t="s">
+        <v>320</v>
+      </c>
+      <c r="E119" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="F119" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G119" s="18" t="s">
         <v>322</v>
       </c>
-      <c r="E119" s="14" t="s">
+      <c r="H119" s="11" t="s">
         <v>323</v>
       </c>
-      <c r="F119" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="G119" s="19" t="s">
+      <c r="I119" s="11" t="s">
         <v>324</v>
       </c>
-      <c r="H119" s="12" t="s">
-        <v>325</v>
-      </c>
-      <c r="I119" s="12" t="s">
-        <v>326</v>
-      </c>
-      <c r="J119" s="18" t="s">
-        <v>158</v>
+      <c r="J119" s="17" t="s">
+        <v>157</v>
       </c>
       <c r="K119" s="5"/>
       <c r="L119" s="5"/>
     </row>
-    <row r="120" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
       <c r="D120" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E120" s="13"/>
+      <c r="E120" s="12"/>
       <c r="F120" s="1"/>
       <c r="G120" s="1"/>
       <c r="H120" s="1"/>
@@ -5352,36 +5347,36 @@
       <c r="K120" s="1"/>
       <c r="L120" s="1"/>
     </row>
-    <row r="121" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A121" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B121" s="5"/>
       <c r="D121" t="s">
-        <v>629</v>
-      </c>
-      <c r="E121" s="14" t="s">
-        <v>630</v>
+        <v>626</v>
+      </c>
+      <c r="E121" s="13" t="s">
+        <v>627</v>
       </c>
       <c r="F121" s="7" t="s">
         <v>145</v>
       </c>
       <c r="G121" s="7" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="H121" s="7" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="I121" s="7" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="J121" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K121" s="5"/>
       <c r="L121" s="5"/>
     </row>
-    <row r="122" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A122" s="2" t="s">
         <v>63</v>
       </c>
@@ -5401,14 +5396,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="123" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
       <c r="D123" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E123" s="13"/>
+      <c r="E123" s="12"/>
       <c r="F123" s="1"/>
       <c r="G123" s="1"/>
       <c r="H123" s="1"/>
@@ -5417,43 +5412,43 @@
       <c r="K123" s="1"/>
       <c r="L123" s="1"/>
     </row>
-    <row r="124" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A124" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B124" s="5"/>
       <c r="D124" t="s">
+        <v>369</v>
+      </c>
+      <c r="E124" s="13" t="s">
+        <v>370</v>
+      </c>
+      <c r="F124" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G124" s="11" t="s">
         <v>371</v>
       </c>
-      <c r="E124" s="14" t="s">
+      <c r="H124" s="11" t="s">
         <v>372</v>
       </c>
-      <c r="F124" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="G124" s="12" t="s">
+      <c r="I124" s="11" t="s">
         <v>373</v>
       </c>
-      <c r="H124" s="12" t="s">
+      <c r="J124" s="17" t="s">
         <v>374</v>
-      </c>
-      <c r="I124" s="12" t="s">
-        <v>375</v>
-      </c>
-      <c r="J124" s="18" t="s">
-        <v>376</v>
       </c>
       <c r="K124" s="5"/>
       <c r="L124" s="5"/>
     </row>
-    <row r="125" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
       <c r="D125" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E125" s="13"/>
+      <c r="E125" s="12"/>
       <c r="F125" s="1"/>
       <c r="G125" s="1"/>
       <c r="H125" s="1"/>
@@ -5462,36 +5457,36 @@
       <c r="K125" s="1"/>
       <c r="L125" s="1"/>
     </row>
-    <row r="126" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A126" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B126" s="5"/>
       <c r="D126" t="s">
-        <v>701</v>
-      </c>
-      <c r="E126" s="14" t="s">
-        <v>702</v>
+        <v>698</v>
+      </c>
+      <c r="E126" s="13" t="s">
+        <v>699</v>
       </c>
       <c r="F126" s="7" t="s">
         <v>149</v>
       </c>
       <c r="G126" s="7" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H126" s="7" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="I126" s="7" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="J126" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="K126" s="5"/>
       <c r="L126" s="5"/>
     </row>
-    <row r="127" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A127" s="2" t="s">
         <v>65</v>
       </c>
@@ -5511,14 +5506,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="128" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
       <c r="D128" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E128" s="13"/>
+      <c r="E128" s="12"/>
       <c r="F128" s="1"/>
       <c r="G128" s="1"/>
       <c r="H128" s="1"/>
@@ -5527,43 +5522,43 @@
       <c r="K128" s="1"/>
       <c r="L128" s="1"/>
     </row>
-    <row r="129" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A129" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B129" s="5"/>
       <c r="D129" t="s">
-        <v>230</v>
-      </c>
-      <c r="E129" s="14" t="s">
-        <v>231</v>
+        <v>228</v>
+      </c>
+      <c r="E129" s="13" t="s">
+        <v>229</v>
       </c>
       <c r="F129" s="7" t="s">
         <v>145</v>
       </c>
       <c r="G129" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="H129" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="I129" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="H129" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="I129" s="7" t="s">
-        <v>234</v>
-      </c>
       <c r="J129" s="6" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="K129" s="5"/>
       <c r="L129" s="5"/>
     </row>
-    <row r="130" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
       <c r="D130" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E130" s="13"/>
+      <c r="E130" s="12"/>
       <c r="F130" s="1"/>
       <c r="G130" s="1"/>
       <c r="H130" s="1"/>
@@ -5572,36 +5567,36 @@
       <c r="K130" s="1"/>
       <c r="L130" s="1"/>
     </row>
-    <row r="131" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A131" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B131" s="5"/>
       <c r="D131" t="s">
+        <v>539</v>
+      </c>
+      <c r="E131" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="F131" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="G131" s="11" t="s">
+        <v>540</v>
+      </c>
+      <c r="H131" s="11" t="s">
         <v>541</v>
       </c>
-      <c r="E131" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="F131" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="G131" s="12" t="s">
+      <c r="I131" s="11" t="s">
         <v>542</v>
       </c>
-      <c r="H131" s="12" t="s">
-        <v>543</v>
-      </c>
-      <c r="I131" s="12" t="s">
-        <v>544</v>
-      </c>
-      <c r="J131" s="18" t="s">
+      <c r="J131" s="17" t="s">
         <v>153</v>
       </c>
       <c r="K131" s="5"/>
       <c r="L131" s="5"/>
     </row>
-    <row r="132" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A132" s="2" t="s">
         <v>67</v>
       </c>
@@ -5621,14 +5616,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="133" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
       <c r="D133" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E133" s="13"/>
+      <c r="E133" s="12"/>
       <c r="F133" s="1"/>
       <c r="G133" s="1"/>
       <c r="H133" s="1"/>
@@ -5637,43 +5632,43 @@
       <c r="K133" s="1"/>
       <c r="L133" s="1"/>
     </row>
-    <row r="134" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A134" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B134" s="5"/>
       <c r="D134" t="s">
-        <v>241</v>
-      </c>
-      <c r="E134" s="14" t="s">
-        <v>242</v>
+        <v>239</v>
+      </c>
+      <c r="E134" s="13" t="s">
+        <v>240</v>
       </c>
       <c r="F134" s="7" t="s">
         <v>149</v>
       </c>
       <c r="G134" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="H134" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="I134" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="H134" s="7" t="s">
-        <v>244</v>
-      </c>
-      <c r="I134" s="7" t="s">
-        <v>245</v>
-      </c>
       <c r="J134" s="6" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="K134" s="5"/>
       <c r="L134" s="5"/>
     </row>
-    <row r="135" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
       <c r="D135" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E135" s="13"/>
+      <c r="E135" s="12"/>
       <c r="F135" s="1"/>
       <c r="G135" s="1"/>
       <c r="H135" s="1"/>
@@ -5682,36 +5677,36 @@
       <c r="K135" s="1"/>
       <c r="L135" s="1"/>
     </row>
-    <row r="136" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A136" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B136" s="5"/>
       <c r="D136" t="s">
-        <v>607</v>
-      </c>
-      <c r="E136" s="14" t="s">
-        <v>608</v>
+        <v>604</v>
+      </c>
+      <c r="E136" s="13" t="s">
+        <v>605</v>
       </c>
       <c r="F136" s="7" t="s">
         <v>145</v>
       </c>
       <c r="G136" s="7" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="H136" s="7" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="I136" s="7" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="J136" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="K136" s="5"/>
       <c r="L136" s="5"/>
     </row>
-    <row r="137" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A137" s="2" t="s">
         <v>69</v>
       </c>
@@ -5731,14 +5726,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="138" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
       <c r="D138" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E138" s="13"/>
+      <c r="E138" s="12"/>
       <c r="F138" s="1"/>
       <c r="G138" s="1"/>
       <c r="H138" s="1"/>
@@ -5747,43 +5742,43 @@
       <c r="K138" s="1"/>
       <c r="L138" s="1"/>
     </row>
-    <row r="139" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A139" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B139" s="5"/>
       <c r="D139" t="s">
+        <v>315</v>
+      </c>
+      <c r="E139" s="13" t="s">
+        <v>316</v>
+      </c>
+      <c r="F139" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G139" s="11" t="s">
         <v>317</v>
       </c>
-      <c r="E139" s="14" t="s">
+      <c r="H139" s="11" t="s">
         <v>318</v>
       </c>
-      <c r="F139" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="G139" s="12" t="s">
+      <c r="I139" s="11" t="s">
         <v>319</v>
       </c>
-      <c r="H139" s="12" t="s">
-        <v>320</v>
-      </c>
-      <c r="I139" s="12" t="s">
-        <v>321</v>
-      </c>
-      <c r="J139" s="18" t="s">
-        <v>163</v>
+      <c r="J139" s="17" t="s">
+        <v>162</v>
       </c>
       <c r="K139" s="5"/>
       <c r="L139" s="5"/>
     </row>
-    <row r="140" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
       <c r="D140" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E140" s="13"/>
+      <c r="E140" s="12"/>
       <c r="F140" s="1"/>
       <c r="G140" s="1"/>
       <c r="H140" s="1"/>
@@ -5792,36 +5787,36 @@
       <c r="K140" s="1"/>
       <c r="L140" s="1"/>
     </row>
-    <row r="141" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A141" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B141" s="5"/>
       <c r="D141" t="s">
-        <v>696</v>
-      </c>
-      <c r="E141" s="14" t="s">
-        <v>697</v>
+        <v>693</v>
+      </c>
+      <c r="E141" s="13" t="s">
+        <v>694</v>
       </c>
       <c r="F141" s="7" t="s">
         <v>145</v>
       </c>
       <c r="G141" s="7" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="H141" s="7" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="I141" s="7" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="J141" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="K141" s="5"/>
       <c r="L141" s="5"/>
     </row>
-    <row r="142" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A142" s="2" t="s">
         <v>71</v>
       </c>
@@ -5841,14 +5836,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="143" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
       <c r="D143" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E143" s="13"/>
+      <c r="E143" s="12"/>
       <c r="F143" s="1"/>
       <c r="G143" s="1"/>
       <c r="H143" s="1"/>
@@ -5857,43 +5852,43 @@
       <c r="K143" s="1"/>
       <c r="L143" s="1"/>
     </row>
-    <row r="144" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A144" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B144" s="5"/>
       <c r="D144" t="s">
+        <v>359</v>
+      </c>
+      <c r="E144" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="F144" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G144" s="11" t="s">
+        <v>360</v>
+      </c>
+      <c r="H144" s="11" t="s">
         <v>361</v>
       </c>
-      <c r="E144" s="14" t="s">
-        <v>263</v>
-      </c>
-      <c r="F144" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="G144" s="12" t="s">
+      <c r="I144" s="11" t="s">
         <v>362</v>
       </c>
-      <c r="H144" s="12" t="s">
-        <v>363</v>
-      </c>
-      <c r="I144" s="12" t="s">
-        <v>364</v>
-      </c>
-      <c r="J144" s="18" t="s">
-        <v>163</v>
+      <c r="J144" s="17" t="s">
+        <v>162</v>
       </c>
       <c r="K144" s="5"/>
       <c r="L144" s="5"/>
     </row>
-    <row r="145" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
       <c r="D145" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E145" s="13"/>
+      <c r="E145" s="12"/>
       <c r="F145" s="1"/>
       <c r="G145" s="1"/>
       <c r="H145" s="1"/>
@@ -5902,36 +5897,36 @@
       <c r="K145" s="1"/>
       <c r="L145" s="1"/>
     </row>
-    <row r="146" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A146" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B146" s="5"/>
       <c r="D146" t="s">
+        <v>470</v>
+      </c>
+      <c r="E146" s="13" t="s">
+        <v>471</v>
+      </c>
+      <c r="F146" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G146" s="11" t="s">
         <v>472</v>
       </c>
-      <c r="E146" s="14" t="s">
+      <c r="H146" s="11" t="s">
         <v>473</v>
       </c>
-      <c r="F146" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="G146" s="12" t="s">
+      <c r="I146" s="11" t="s">
         <v>474</v>
       </c>
-      <c r="H146" s="12" t="s">
-        <v>475</v>
-      </c>
-      <c r="I146" s="12" t="s">
-        <v>476</v>
-      </c>
-      <c r="J146" s="18" t="s">
-        <v>198</v>
+      <c r="J146" s="17" t="s">
+        <v>196</v>
       </c>
       <c r="K146" s="5"/>
       <c r="L146" s="5"/>
     </row>
-    <row r="147" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A147" s="2" t="s">
         <v>73</v>
       </c>
@@ -5951,14 +5946,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="148" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
       <c r="D148" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E148" s="13"/>
+      <c r="E148" s="12"/>
       <c r="F148" s="1"/>
       <c r="G148" s="1"/>
       <c r="H148" s="1"/>
@@ -5967,43 +5962,43 @@
       <c r="K148" s="1"/>
       <c r="L148" s="1"/>
     </row>
-    <row r="149" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A149" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B149" s="5"/>
       <c r="D149" t="s">
-        <v>682</v>
-      </c>
-      <c r="E149" s="14" t="s">
-        <v>411</v>
+        <v>679</v>
+      </c>
+      <c r="E149" s="13" t="s">
+        <v>409</v>
       </c>
       <c r="F149" s="7" t="s">
         <v>145</v>
       </c>
       <c r="G149" s="7" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="H149" s="7" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="I149" s="7" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="J149" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="K149" s="5"/>
       <c r="L149" s="5"/>
     </row>
-    <row r="150" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
       <c r="D150" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E150" s="13"/>
+      <c r="E150" s="12"/>
       <c r="F150" s="1"/>
       <c r="G150" s="1"/>
       <c r="H150" s="1"/>
@@ -6012,36 +6007,36 @@
       <c r="K150" s="1"/>
       <c r="L150" s="1"/>
     </row>
-    <row r="151" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A151" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B151" s="5"/>
       <c r="D151" t="s">
-        <v>686</v>
-      </c>
-      <c r="E151" s="14" t="s">
-        <v>645</v>
+        <v>683</v>
+      </c>
+      <c r="E151" s="13" t="s">
+        <v>642</v>
       </c>
       <c r="F151" s="7" t="s">
         <v>149</v>
       </c>
       <c r="G151" s="7" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="H151" s="7" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="I151" s="7" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="J151" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="K151" s="5"/>
       <c r="L151" s="5"/>
     </row>
-    <row r="152" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A152" s="2" t="s">
         <v>75</v>
       </c>
@@ -6061,14 +6056,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="153" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
       <c r="D153" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E153" s="13"/>
+      <c r="E153" s="12"/>
       <c r="F153" s="1"/>
       <c r="G153" s="1"/>
       <c r="H153" s="1"/>
@@ -6077,43 +6072,43 @@
       <c r="K153" s="1"/>
       <c r="L153" s="1"/>
     </row>
-    <row r="154" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A154" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B154" s="5"/>
       <c r="D154" t="s">
+        <v>279</v>
+      </c>
+      <c r="E154" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="F154" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G154" s="11" t="s">
+        <v>280</v>
+      </c>
+      <c r="H154" s="11" t="s">
         <v>281</v>
       </c>
-      <c r="E154" s="14" t="s">
-        <v>183</v>
-      </c>
-      <c r="F154" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="G154" s="12" t="s">
+      <c r="I154" s="11" t="s">
         <v>282</v>
       </c>
-      <c r="H154" s="12" t="s">
+      <c r="J154" s="17" t="s">
         <v>283</v>
-      </c>
-      <c r="I154" s="12" t="s">
-        <v>284</v>
-      </c>
-      <c r="J154" s="18" t="s">
-        <v>285</v>
       </c>
       <c r="K154" s="5"/>
       <c r="L154" s="5"/>
     </row>
-    <row r="155" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
       <c r="D155" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E155" s="13"/>
+      <c r="E155" s="12"/>
       <c r="F155" s="1"/>
       <c r="G155" s="1"/>
       <c r="H155" s="1"/>
@@ -6122,36 +6117,36 @@
       <c r="K155" s="1"/>
       <c r="L155" s="1"/>
     </row>
-    <row r="156" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A156" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B156" s="5"/>
       <c r="D156" t="s">
-        <v>625</v>
-      </c>
-      <c r="E156" s="14" t="s">
-        <v>453</v>
+        <v>622</v>
+      </c>
+      <c r="E156" s="13" t="s">
+        <v>451</v>
       </c>
       <c r="F156" s="7" t="s">
         <v>149</v>
       </c>
       <c r="G156" s="7" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="H156" s="7" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="I156" s="7" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="J156" s="6" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="K156" s="5"/>
       <c r="L156" s="5"/>
     </row>
-    <row r="157" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A157" s="2" t="s">
         <v>77</v>
       </c>
@@ -6171,14 +6166,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="158" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
       <c r="D158" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E158" s="13"/>
+      <c r="E158" s="12"/>
       <c r="F158" s="1"/>
       <c r="G158" s="1"/>
       <c r="H158" s="1"/>
@@ -6187,43 +6182,43 @@
       <c r="K158" s="1"/>
       <c r="L158" s="1"/>
     </row>
-    <row r="159" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A159" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B159" s="5"/>
       <c r="D159" t="s">
+        <v>490</v>
+      </c>
+      <c r="E159" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="F159" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G159" s="11" t="s">
+        <v>491</v>
+      </c>
+      <c r="H159" s="11" t="s">
         <v>492</v>
       </c>
-      <c r="E159" s="14" t="s">
-        <v>323</v>
-      </c>
-      <c r="F159" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="G159" s="12" t="s">
+      <c r="I159" s="11" t="s">
         <v>493</v>
       </c>
-      <c r="H159" s="12" t="s">
+      <c r="J159" s="17" t="s">
         <v>494</v>
-      </c>
-      <c r="I159" s="12" t="s">
-        <v>495</v>
-      </c>
-      <c r="J159" s="18" t="s">
-        <v>496</v>
       </c>
       <c r="K159" s="5"/>
       <c r="L159" s="5"/>
     </row>
-    <row r="160" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
       <c r="D160" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E160" s="13"/>
+      <c r="E160" s="12"/>
       <c r="F160" s="1"/>
       <c r="G160" s="1"/>
       <c r="H160" s="1"/>
@@ -6232,36 +6227,36 @@
       <c r="K160" s="1"/>
       <c r="L160" s="1"/>
     </row>
-    <row r="161" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A161" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B161" s="5"/>
       <c r="D161" t="s">
-        <v>693</v>
-      </c>
-      <c r="E161" s="14" t="s">
-        <v>473</v>
+        <v>690</v>
+      </c>
+      <c r="E161" s="13" t="s">
+        <v>471</v>
       </c>
       <c r="F161" s="7" t="s">
         <v>149</v>
       </c>
       <c r="G161" s="7" t="s">
-        <v>694</v>
-      </c>
-      <c r="H161" s="8" t="s">
-        <v>715</v>
+        <v>691</v>
+      </c>
+      <c r="H161" s="7" t="s">
+        <v>712</v>
       </c>
       <c r="I161" s="7" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="J161" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="K161" s="5"/>
       <c r="L161" s="5"/>
     </row>
-    <row r="162" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A162" s="2" t="s">
         <v>79</v>
       </c>
@@ -6281,14 +6276,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="163" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
       <c r="D163" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E163" s="13"/>
+      <c r="E163" s="12"/>
       <c r="F163" s="1"/>
       <c r="G163" s="1"/>
       <c r="H163" s="1"/>
@@ -6297,43 +6292,43 @@
       <c r="K163" s="1"/>
       <c r="L163" s="1"/>
     </row>
-    <row r="164" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A164" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B164" s="5"/>
       <c r="D164" t="s">
+        <v>274</v>
+      </c>
+      <c r="E164" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="F164" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="G164" s="11" t="s">
         <v>276</v>
       </c>
-      <c r="E164" s="14" t="s">
+      <c r="H164" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="F164" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="G164" s="12" t="s">
+      <c r="I164" s="11" t="s">
         <v>278</v>
       </c>
-      <c r="H164" s="12" t="s">
-        <v>279</v>
-      </c>
-      <c r="I164" s="12" t="s">
-        <v>280</v>
-      </c>
-      <c r="J164" s="18" t="s">
-        <v>163</v>
+      <c r="J164" s="17" t="s">
+        <v>162</v>
       </c>
       <c r="K164" s="5"/>
       <c r="L164" s="5"/>
     </row>
-    <row r="165" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
       <c r="D165" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E165" s="13"/>
+      <c r="E165" s="12"/>
       <c r="F165" s="1"/>
       <c r="G165" s="1"/>
       <c r="H165" s="1"/>
@@ -6342,36 +6337,36 @@
       <c r="K165" s="1"/>
       <c r="L165" s="1"/>
     </row>
-    <row r="166" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A166" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B166" s="5"/>
       <c r="D166" t="s">
+        <v>553</v>
+      </c>
+      <c r="E166" s="13" t="s">
+        <v>554</v>
+      </c>
+      <c r="F166" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G166" s="11" t="s">
         <v>555</v>
       </c>
-      <c r="E166" s="14" t="s">
+      <c r="H166" s="11" t="s">
         <v>556</v>
       </c>
-      <c r="F166" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="G166" s="12" t="s">
+      <c r="I166" s="11" t="s">
         <v>557</v>
       </c>
-      <c r="H166" s="12" t="s">
-        <v>558</v>
-      </c>
-      <c r="I166" s="12" t="s">
-        <v>559</v>
-      </c>
-      <c r="J166" s="18" t="s">
-        <v>376</v>
+      <c r="J166" s="17" t="s">
+        <v>374</v>
       </c>
       <c r="K166" s="5"/>
       <c r="L166" s="5"/>
     </row>
-    <row r="167" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A167" s="2" t="s">
         <v>81</v>
       </c>
@@ -6391,14 +6386,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="168" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
       <c r="D168" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E168" s="13"/>
+      <c r="E168" s="12"/>
       <c r="F168" s="1"/>
       <c r="G168" s="1"/>
       <c r="H168" s="1"/>
@@ -6407,43 +6402,43 @@
       <c r="K168" s="1"/>
       <c r="L168" s="1"/>
     </row>
-    <row r="169" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A169" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B169" s="5"/>
       <c r="D169" t="s">
+        <v>390</v>
+      </c>
+      <c r="E169" s="13" t="s">
+        <v>300</v>
+      </c>
+      <c r="F169" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="G169" s="11" t="s">
+        <v>391</v>
+      </c>
+      <c r="H169" s="11" t="s">
         <v>392</v>
       </c>
-      <c r="E169" s="14" t="s">
-        <v>302</v>
-      </c>
-      <c r="F169" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="G169" s="12" t="s">
+      <c r="I169" s="11" t="s">
         <v>393</v>
       </c>
-      <c r="H169" s="12" t="s">
-        <v>394</v>
-      </c>
-      <c r="I169" s="12" t="s">
-        <v>395</v>
-      </c>
-      <c r="J169" s="18" t="s">
-        <v>376</v>
+      <c r="J169" s="17" t="s">
+        <v>374</v>
       </c>
       <c r="K169" s="5"/>
       <c r="L169" s="5"/>
     </row>
-    <row r="170" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
       <c r="D170" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E170" s="13"/>
+      <c r="E170" s="12"/>
       <c r="F170" s="1"/>
       <c r="G170" s="1"/>
       <c r="H170" s="1"/>
@@ -6452,36 +6447,36 @@
       <c r="K170" s="1"/>
       <c r="L170" s="1"/>
     </row>
-    <row r="171" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A171" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B171" s="5"/>
       <c r="D171" t="s">
+        <v>534</v>
+      </c>
+      <c r="E171" s="13" t="s">
+        <v>535</v>
+      </c>
+      <c r="F171" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G171" s="11" t="s">
         <v>536</v>
       </c>
-      <c r="E171" s="14" t="s">
+      <c r="H171" s="11" t="s">
         <v>537</v>
       </c>
-      <c r="F171" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="G171" s="12" t="s">
+      <c r="I171" s="11" t="s">
         <v>538</v>
       </c>
-      <c r="H171" s="12" t="s">
-        <v>539</v>
-      </c>
-      <c r="I171" s="12" t="s">
-        <v>540</v>
-      </c>
-      <c r="J171" s="18" t="s">
-        <v>198</v>
+      <c r="J171" s="17" t="s">
+        <v>196</v>
       </c>
       <c r="K171" s="5"/>
       <c r="L171" s="5"/>
     </row>
-    <row r="172" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A172" s="2" t="s">
         <v>83</v>
       </c>
@@ -6501,14 +6496,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="173" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
       <c r="D173" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E173" s="13"/>
+      <c r="E173" s="12"/>
       <c r="F173" s="1"/>
       <c r="G173" s="1"/>
       <c r="H173" s="1"/>
@@ -6517,43 +6512,43 @@
       <c r="K173" s="1"/>
       <c r="L173" s="1"/>
     </row>
-    <row r="174" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A174" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B174" s="5"/>
       <c r="D174" t="s">
-        <v>193</v>
-      </c>
-      <c r="E174" s="14" t="s">
-        <v>194</v>
+        <v>191</v>
+      </c>
+      <c r="E174" s="13" t="s">
+        <v>192</v>
       </c>
       <c r="F174" s="7" t="s">
         <v>145</v>
       </c>
       <c r="G174" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="H174" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="I174" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="H174" s="7" t="s">
+      <c r="J174" s="6" t="s">
         <v>196</v>
-      </c>
-      <c r="I174" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="J174" s="6" t="s">
-        <v>198</v>
       </c>
       <c r="K174" s="5"/>
       <c r="L174" s="5"/>
     </row>
-    <row r="175" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
       <c r="D175" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E175" s="13"/>
+      <c r="E175" s="12"/>
       <c r="F175" s="1"/>
       <c r="G175" s="1"/>
       <c r="H175" s="1"/>
@@ -6562,36 +6557,36 @@
       <c r="K175" s="1"/>
       <c r="L175" s="1"/>
     </row>
-    <row r="176" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:12" ht="24" x14ac:dyDescent="0.2">
       <c r="A176" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B176" s="5"/>
       <c r="D176" t="s">
+        <v>576</v>
+      </c>
+      <c r="E176" s="20" t="s">
+        <v>577</v>
+      </c>
+      <c r="F176" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G176" s="11" t="s">
         <v>578</v>
       </c>
-      <c r="E176" s="21" t="s">
+      <c r="H176" s="11" t="s">
         <v>579</v>
       </c>
-      <c r="F176" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="G176" s="12" t="s">
+      <c r="I176" s="11" t="s">
         <v>580</v>
       </c>
-      <c r="H176" s="12" t="s">
-        <v>581</v>
-      </c>
-      <c r="I176" s="12" t="s">
-        <v>582</v>
-      </c>
-      <c r="J176" s="18" t="s">
-        <v>163</v>
+      <c r="J176" s="17" t="s">
+        <v>162</v>
       </c>
       <c r="K176" s="5"/>
       <c r="L176" s="5"/>
     </row>
-    <row r="177" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A177" s="2" t="s">
         <v>85</v>
       </c>
@@ -6611,14 +6606,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="178" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
       <c r="D178" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E178" s="13"/>
+      <c r="E178" s="12"/>
       <c r="F178" s="1"/>
       <c r="G178" s="1"/>
       <c r="H178" s="1"/>
@@ -6627,43 +6622,43 @@
       <c r="K178" s="1"/>
       <c r="L178" s="1"/>
     </row>
-    <row r="179" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A179" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B179" s="5"/>
       <c r="D179" t="s">
+        <v>404</v>
+      </c>
+      <c r="E179" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="F179" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G179" s="11" t="s">
+        <v>405</v>
+      </c>
+      <c r="H179" s="11" t="s">
         <v>406</v>
       </c>
-      <c r="E179" s="14" t="s">
-        <v>183</v>
-      </c>
-      <c r="F179" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="G179" s="12" t="s">
+      <c r="I179" s="11" t="s">
         <v>407</v>
       </c>
-      <c r="H179" s="12" t="s">
-        <v>408</v>
-      </c>
-      <c r="I179" s="12" t="s">
-        <v>409</v>
-      </c>
-      <c r="J179" s="18" t="s">
-        <v>163</v>
+      <c r="J179" s="17" t="s">
+        <v>162</v>
       </c>
       <c r="K179" s="5"/>
       <c r="L179" s="5"/>
     </row>
-    <row r="180" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
       <c r="D180" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E180" s="13"/>
+      <c r="E180" s="12"/>
       <c r="F180" s="1"/>
       <c r="G180" s="1"/>
       <c r="H180" s="1"/>
@@ -6672,36 +6667,36 @@
       <c r="K180" s="1"/>
       <c r="L180" s="1"/>
     </row>
-    <row r="181" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A181" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B181" s="5"/>
       <c r="D181" t="s">
+        <v>721</v>
+      </c>
+      <c r="E181" s="13" t="s">
+        <v>581</v>
+      </c>
+      <c r="F181" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G181" s="11" t="s">
+        <v>582</v>
+      </c>
+      <c r="H181" s="11" t="s">
         <v>583</v>
       </c>
-      <c r="E181" s="14" t="s">
+      <c r="I181" s="11" t="s">
         <v>584</v>
       </c>
-      <c r="F181" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="G181" s="12" t="s">
-        <v>585</v>
-      </c>
-      <c r="H181" s="12" t="s">
-        <v>586</v>
-      </c>
-      <c r="I181" s="12" t="s">
-        <v>587</v>
-      </c>
-      <c r="J181" s="18" t="s">
-        <v>198</v>
+      <c r="J181" s="17" t="s">
+        <v>196</v>
       </c>
       <c r="K181" s="5"/>
       <c r="L181" s="5"/>
     </row>
-    <row r="182" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A182" s="2" t="s">
         <v>87</v>
       </c>
@@ -6721,14 +6716,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="183" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
       <c r="D183" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E183" s="13"/>
+      <c r="E183" s="12"/>
       <c r="F183" s="1"/>
       <c r="G183" s="1"/>
       <c r="H183" s="1"/>
@@ -6737,43 +6732,43 @@
       <c r="K183" s="1"/>
       <c r="L183" s="1"/>
     </row>
-    <row r="184" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A184" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B184" s="5"/>
       <c r="D184" t="s">
+        <v>408</v>
+      </c>
+      <c r="E184" s="13" t="s">
+        <v>409</v>
+      </c>
+      <c r="F184" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G184" s="11" t="s">
         <v>410</v>
       </c>
-      <c r="E184" s="14" t="s">
+      <c r="H184" s="11" t="s">
         <v>411</v>
       </c>
-      <c r="F184" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="G184" s="12" t="s">
+      <c r="I184" s="11" t="s">
         <v>412</v>
       </c>
-      <c r="H184" s="12" t="s">
-        <v>413</v>
-      </c>
-      <c r="I184" s="12" t="s">
-        <v>414</v>
-      </c>
-      <c r="J184" s="18" t="s">
-        <v>163</v>
+      <c r="J184" s="17" t="s">
+        <v>162</v>
       </c>
       <c r="K184" s="5"/>
       <c r="L184" s="5"/>
     </row>
-    <row r="185" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
       <c r="D185" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E185" s="13"/>
+      <c r="E185" s="12"/>
       <c r="F185" s="1"/>
       <c r="G185" s="1"/>
       <c r="H185" s="1"/>
@@ -6782,36 +6777,36 @@
       <c r="K185" s="1"/>
       <c r="L185" s="1"/>
     </row>
-    <row r="186" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A186" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B186" s="5"/>
       <c r="D186" t="s">
+        <v>585</v>
+      </c>
+      <c r="E186" s="13" t="s">
+        <v>586</v>
+      </c>
+      <c r="F186" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G186" s="11" t="s">
+        <v>587</v>
+      </c>
+      <c r="H186" s="11" t="s">
         <v>588</v>
       </c>
-      <c r="E186" s="14" t="s">
+      <c r="I186" s="11" t="s">
         <v>589</v>
       </c>
-      <c r="F186" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="G186" s="12" t="s">
-        <v>590</v>
-      </c>
-      <c r="H186" s="12" t="s">
-        <v>591</v>
-      </c>
-      <c r="I186" s="12" t="s">
-        <v>592</v>
-      </c>
-      <c r="J186" s="18" t="s">
-        <v>572</v>
+      <c r="J186" s="17" t="s">
+        <v>570</v>
       </c>
       <c r="K186" s="5"/>
       <c r="L186" s="5"/>
     </row>
-    <row r="187" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A187" s="2" t="s">
         <v>89</v>
       </c>
@@ -6831,14 +6826,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="188" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
       <c r="D188" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E188" s="13"/>
+      <c r="E188" s="12"/>
       <c r="F188" s="1"/>
       <c r="G188" s="1"/>
       <c r="H188" s="1"/>
@@ -6847,12 +6842,12 @@
       <c r="K188" s="1"/>
       <c r="L188" s="1"/>
     </row>
-    <row r="189" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A189" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B189" s="5"/>
-      <c r="E189" s="14"/>
+      <c r="E189" s="13"/>
       <c r="F189" s="5"/>
       <c r="G189" s="5"/>
       <c r="H189" s="5"/>
@@ -6861,14 +6856,14 @@
       <c r="K189" s="5"/>
       <c r="L189" s="5"/>
     </row>
-    <row r="190" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
       <c r="D190" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E190" s="13"/>
+      <c r="E190" s="12"/>
       <c r="F190" s="1"/>
       <c r="G190" s="1"/>
       <c r="H190" s="1"/>
@@ -6877,12 +6872,12 @@
       <c r="K190" s="1"/>
       <c r="L190" s="1"/>
     </row>
-    <row r="191" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A191" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B191" s="5"/>
-      <c r="E191" s="14"/>
+      <c r="E191" s="13"/>
       <c r="F191" s="5"/>
       <c r="G191" s="5"/>
       <c r="H191" s="5"/>
@@ -6891,7 +6886,7 @@
       <c r="K191" s="5"/>
       <c r="L191" s="5"/>
     </row>
-    <row r="192" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A192" s="2" t="s">
         <v>91</v>
       </c>
@@ -6911,14 +6906,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="193" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
       <c r="D193" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E193" s="13"/>
+      <c r="E193" s="12"/>
       <c r="F193" s="1"/>
       <c r="G193" s="1"/>
       <c r="H193" s="1"/>
@@ -6927,43 +6922,43 @@
       <c r="K193" s="1"/>
       <c r="L193" s="1"/>
     </row>
-    <row r="194" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A194" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B194" s="5"/>
       <c r="D194" t="s">
+        <v>330</v>
+      </c>
+      <c r="E194" s="13" t="s">
+        <v>331</v>
+      </c>
+      <c r="F194" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="G194" s="11" t="s">
         <v>332</v>
       </c>
-      <c r="E194" s="14" t="s">
+      <c r="H194" s="11" t="s">
         <v>333</v>
       </c>
-      <c r="F194" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="G194" s="12" t="s">
+      <c r="I194" s="11" t="s">
         <v>334</v>
       </c>
-      <c r="H194" s="12" t="s">
-        <v>335</v>
-      </c>
-      <c r="I194" s="12" t="s">
-        <v>336</v>
-      </c>
-      <c r="J194" s="18" t="s">
+      <c r="J194" s="17" t="s">
         <v>153</v>
       </c>
       <c r="K194" s="5"/>
       <c r="L194" s="5"/>
     </row>
-    <row r="195" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
       <c r="D195" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E195" s="13"/>
+      <c r="E195" s="12"/>
       <c r="F195" s="1"/>
       <c r="G195" s="1"/>
       <c r="H195" s="1"/>
@@ -6972,36 +6967,36 @@
       <c r="K195" s="1"/>
       <c r="L195" s="1"/>
     </row>
-    <row r="196" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A196" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B196" s="5"/>
       <c r="D196" t="s">
+        <v>520</v>
+      </c>
+      <c r="E196" s="13" t="s">
+        <v>521</v>
+      </c>
+      <c r="F196" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="G196" s="11" t="s">
         <v>522</v>
       </c>
-      <c r="E196" s="14" t="s">
+      <c r="H196" s="11" t="s">
         <v>523</v>
       </c>
-      <c r="F196" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="G196" s="12" t="s">
+      <c r="I196" s="11" t="s">
         <v>524</v>
       </c>
-      <c r="H196" s="12" t="s">
-        <v>525</v>
-      </c>
-      <c r="I196" s="12" t="s">
-        <v>526</v>
-      </c>
-      <c r="J196" s="18" t="s">
-        <v>198</v>
+      <c r="J196" s="17" t="s">
+        <v>196</v>
       </c>
       <c r="K196" s="5"/>
       <c r="L196" s="5"/>
     </row>
-    <row r="197" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A197" s="2" t="s">
         <v>93</v>
       </c>
@@ -7021,14 +7016,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="198" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
       <c r="D198" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E198" s="13"/>
+      <c r="E198" s="12"/>
       <c r="F198" s="1"/>
       <c r="G198" s="1"/>
       <c r="H198" s="1"/>
@@ -7037,43 +7032,43 @@
       <c r="K198" s="1"/>
       <c r="L198" s="1"/>
     </row>
-    <row r="199" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A199" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B199" s="5"/>
       <c r="D199" t="s">
-        <v>199</v>
-      </c>
-      <c r="E199" s="14" t="s">
-        <v>200</v>
+        <v>197</v>
+      </c>
+      <c r="E199" s="13" t="s">
+        <v>198</v>
       </c>
       <c r="F199" s="7" t="s">
         <v>145</v>
       </c>
       <c r="G199" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="H199" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="I199" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="H199" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="I199" s="7" t="s">
-        <v>203</v>
-      </c>
       <c r="J199" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="K199" s="5"/>
       <c r="L199" s="5"/>
     </row>
-    <row r="200" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
       <c r="D200" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E200" s="13"/>
+      <c r="E200" s="12"/>
       <c r="F200" s="1"/>
       <c r="G200" s="1"/>
       <c r="H200" s="1"/>
@@ -7082,36 +7077,36 @@
       <c r="K200" s="1"/>
       <c r="L200" s="1"/>
     </row>
-    <row r="201" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A201" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B201" s="5"/>
       <c r="D201" t="s">
+        <v>515</v>
+      </c>
+      <c r="E201" s="13" t="s">
+        <v>381</v>
+      </c>
+      <c r="F201" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="G201" s="11" t="s">
+        <v>516</v>
+      </c>
+      <c r="H201" s="11" t="s">
         <v>517</v>
       </c>
-      <c r="E201" s="14" t="s">
-        <v>383</v>
-      </c>
-      <c r="F201" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="G201" s="12" t="s">
+      <c r="I201" s="11" t="s">
         <v>518</v>
       </c>
-      <c r="H201" s="12" t="s">
+      <c r="J201" s="17" t="s">
         <v>519</v>
-      </c>
-      <c r="I201" s="12" t="s">
-        <v>520</v>
-      </c>
-      <c r="J201" s="18" t="s">
-        <v>521</v>
       </c>
       <c r="K201" s="5"/>
       <c r="L201" s="5"/>
     </row>
-    <row r="202" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A202" s="2" t="s">
         <v>95</v>
       </c>
@@ -7131,14 +7126,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="203" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
       <c r="D203" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E203" s="13"/>
+      <c r="E203" s="12"/>
       <c r="F203" s="1"/>
       <c r="G203" s="1"/>
       <c r="H203" s="1"/>
@@ -7147,43 +7142,43 @@
       <c r="K203" s="1"/>
       <c r="L203" s="1"/>
     </row>
-    <row r="204" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A204" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B204" s="5"/>
       <c r="D204" t="s">
+        <v>255</v>
+      </c>
+      <c r="E204" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="F204" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="G204" s="11" t="s">
         <v>257</v>
       </c>
-      <c r="E204" s="14" t="s">
+      <c r="H204" s="11" t="s">
         <v>258</v>
       </c>
-      <c r="F204" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="G204" s="12" t="s">
+      <c r="I204" s="11" t="s">
         <v>259</v>
       </c>
-      <c r="H204" s="12" t="s">
-        <v>260</v>
-      </c>
-      <c r="I204" s="12" t="s">
-        <v>261</v>
-      </c>
-      <c r="J204" s="18" t="s">
-        <v>187</v>
+      <c r="J204" s="17" t="s">
+        <v>185</v>
       </c>
       <c r="K204" s="5"/>
       <c r="L204" s="5"/>
     </row>
-    <row r="205" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
       <c r="D205" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E205" s="13"/>
+      <c r="E205" s="12"/>
       <c r="F205" s="1"/>
       <c r="G205" s="1"/>
       <c r="H205" s="1"/>
@@ -7192,36 +7187,36 @@
       <c r="K205" s="1"/>
       <c r="L205" s="1"/>
     </row>
-    <row r="206" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:12" ht="24" x14ac:dyDescent="0.2">
       <c r="A206" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B206" s="5"/>
       <c r="D206" t="s">
+        <v>571</v>
+      </c>
+      <c r="E206" s="20" t="s">
+        <v>574</v>
+      </c>
+      <c r="F206" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G206" s="11" t="s">
+        <v>572</v>
+      </c>
+      <c r="H206" s="11" t="s">
         <v>573</v>
       </c>
-      <c r="E206" s="21" t="s">
-        <v>576</v>
-      </c>
-      <c r="F206" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="G206" s="12" t="s">
-        <v>574</v>
-      </c>
-      <c r="H206" s="12" t="s">
+      <c r="I206" s="11" t="s">
         <v>575</v>
       </c>
-      <c r="I206" s="12" t="s">
-        <v>577</v>
-      </c>
-      <c r="J206" s="18" t="s">
-        <v>311</v>
+      <c r="J206" s="17" t="s">
+        <v>309</v>
       </c>
       <c r="K206" s="5"/>
       <c r="L206" s="5"/>
     </row>
-    <row r="207" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A207" s="2" t="s">
         <v>97</v>
       </c>
@@ -7241,14 +7236,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="208" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
       <c r="D208" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E208" s="13"/>
+      <c r="E208" s="12"/>
       <c r="F208" s="1"/>
       <c r="G208" s="1"/>
       <c r="H208" s="1"/>
@@ -7257,43 +7252,43 @@
       <c r="K208" s="1"/>
       <c r="L208" s="1"/>
     </row>
-    <row r="209" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A209" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B209" s="5"/>
       <c r="D209" t="s">
+        <v>299</v>
+      </c>
+      <c r="E209" s="15" t="s">
+        <v>300</v>
+      </c>
+      <c r="F209" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G209" s="11" t="s">
         <v>301</v>
       </c>
-      <c r="E209" s="16" t="s">
+      <c r="H209" s="11" t="s">
         <v>302</v>
       </c>
-      <c r="F209" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="G209" s="12" t="s">
+      <c r="I209" s="11" t="s">
         <v>303</v>
       </c>
-      <c r="H209" s="12" t="s">
-        <v>304</v>
-      </c>
-      <c r="I209" s="12" t="s">
-        <v>305</v>
-      </c>
-      <c r="J209" s="18" t="s">
-        <v>163</v>
+      <c r="J209" s="17" t="s">
+        <v>162</v>
       </c>
       <c r="K209" s="5"/>
       <c r="L209" s="5"/>
     </row>
-    <row r="210" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
       <c r="D210" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E210" s="13"/>
+      <c r="E210" s="12"/>
       <c r="F210" s="1"/>
       <c r="G210" s="1"/>
       <c r="H210" s="1"/>
@@ -7302,12 +7297,12 @@
       <c r="K210" s="1"/>
       <c r="L210" s="1"/>
     </row>
-    <row r="211" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A211" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B211" s="5"/>
-      <c r="E211" s="14"/>
+      <c r="E211" s="13"/>
       <c r="F211" s="5"/>
       <c r="G211" s="5"/>
       <c r="H211" s="5"/>
@@ -7316,7 +7311,7 @@
       <c r="K211" s="5"/>
       <c r="L211" s="5"/>
     </row>
-    <row r="212" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A212" s="2" t="s">
         <v>99</v>
       </c>
@@ -7336,14 +7331,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="213" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
       <c r="D213" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E213" s="13"/>
+      <c r="E213" s="12"/>
       <c r="F213" s="1"/>
       <c r="G213" s="1"/>
       <c r="H213" s="1"/>
@@ -7352,43 +7347,43 @@
       <c r="K213" s="1"/>
       <c r="L213" s="1"/>
     </row>
-    <row r="214" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A214" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B214" s="5"/>
       <c r="D214" t="s">
-        <v>246</v>
-      </c>
-      <c r="E214" s="14" t="s">
-        <v>247</v>
+        <v>244</v>
+      </c>
+      <c r="E214" s="13" t="s">
+        <v>245</v>
       </c>
       <c r="F214" s="7" t="s">
         <v>145</v>
       </c>
       <c r="G214" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="H214" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="I214" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="H214" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="I214" s="7" t="s">
-        <v>250</v>
-      </c>
       <c r="J214" s="6" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="K214" s="5"/>
       <c r="L214" s="5"/>
     </row>
-    <row r="215" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
       <c r="D215" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E215" s="13"/>
+      <c r="E215" s="12"/>
       <c r="F215" s="1"/>
       <c r="G215" s="1"/>
       <c r="H215" s="1"/>
@@ -7397,28 +7392,28 @@
       <c r="K215" s="1"/>
       <c r="L215" s="1"/>
     </row>
-    <row r="216" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A216" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B216" s="5"/>
       <c r="D216" t="s">
-        <v>668</v>
-      </c>
-      <c r="E216" s="14" t="s">
-        <v>669</v>
+        <v>665</v>
+      </c>
+      <c r="E216" s="13" t="s">
+        <v>666</v>
       </c>
       <c r="F216" s="7" t="s">
         <v>145</v>
       </c>
       <c r="G216" s="7" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="H216" s="7" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="I216" s="7" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="J216" s="6" t="s">
         <v>153</v>
@@ -7426,7 +7421,7 @@
       <c r="K216" s="5"/>
       <c r="L216" s="5"/>
     </row>
-    <row r="217" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A217" s="2" t="s">
         <v>101</v>
       </c>
@@ -7446,14 +7441,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="218" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
       <c r="D218" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E218" s="13"/>
+      <c r="E218" s="12"/>
       <c r="F218" s="1"/>
       <c r="G218" s="1"/>
       <c r="H218" s="1"/>
@@ -7462,43 +7457,43 @@
       <c r="K218" s="1"/>
       <c r="L218" s="1"/>
     </row>
-    <row r="219" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A219" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B219" s="5"/>
       <c r="D219" t="s">
-        <v>658</v>
-      </c>
-      <c r="E219" s="14" t="s">
-        <v>659</v>
+        <v>655</v>
+      </c>
+      <c r="E219" s="13" t="s">
+        <v>656</v>
       </c>
       <c r="F219" s="7" t="s">
         <v>145</v>
       </c>
       <c r="G219" s="7" t="s">
+        <v>657</v>
+      </c>
+      <c r="H219" s="7" t="s">
+        <v>658</v>
+      </c>
+      <c r="I219" s="7" t="s">
+        <v>659</v>
+      </c>
+      <c r="J219" s="6" t="s">
         <v>660</v>
-      </c>
-      <c r="H219" s="7" t="s">
-        <v>661</v>
-      </c>
-      <c r="I219" s="7" t="s">
-        <v>662</v>
-      </c>
-      <c r="J219" s="6" t="s">
-        <v>663</v>
       </c>
       <c r="K219" s="5"/>
       <c r="L219" s="5"/>
     </row>
-    <row r="220" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
       <c r="D220" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E220" s="13"/>
+      <c r="E220" s="12"/>
       <c r="F220" s="1"/>
       <c r="G220" s="1"/>
       <c r="H220" s="1"/>
@@ -7507,36 +7502,36 @@
       <c r="K220" s="1"/>
       <c r="L220" s="1"/>
     </row>
-    <row r="221" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A221" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B221" s="5"/>
       <c r="D221" t="s">
-        <v>717</v>
-      </c>
-      <c r="E221" s="14" t="s">
-        <v>718</v>
+        <v>714</v>
+      </c>
+      <c r="E221" s="13" t="s">
+        <v>715</v>
       </c>
       <c r="F221" s="7" t="s">
         <v>145</v>
       </c>
       <c r="G221" s="7" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="H221" s="7" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="I221" s="5" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="J221" s="6" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="K221" s="5"/>
       <c r="L221" s="5"/>
     </row>
-    <row r="222" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A222" s="2" t="s">
         <v>103</v>
       </c>
@@ -7556,14 +7551,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="223" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
       <c r="D223" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E223" s="13"/>
+      <c r="E223" s="12"/>
       <c r="F223" s="1"/>
       <c r="G223" s="1"/>
       <c r="H223" s="1"/>
@@ -7572,43 +7567,43 @@
       <c r="K223" s="1"/>
       <c r="L223" s="1"/>
     </row>
-    <row r="224" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A224" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B224" s="5"/>
       <c r="D224" t="s">
-        <v>653</v>
-      </c>
-      <c r="E224" s="14" t="s">
-        <v>654</v>
+        <v>650</v>
+      </c>
+      <c r="E224" s="13" t="s">
+        <v>651</v>
       </c>
       <c r="F224" s="7" t="s">
         <v>149</v>
       </c>
       <c r="G224" s="7" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="H224" s="7" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="I224" s="7" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="J224" s="6" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="K224" s="5"/>
       <c r="L224" s="5"/>
     </row>
-    <row r="225" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
       <c r="D225" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E225" s="13"/>
+      <c r="E225" s="12"/>
       <c r="F225" s="1"/>
       <c r="G225" s="1"/>
       <c r="H225" s="1"/>
@@ -7617,36 +7612,36 @@
       <c r="K225" s="1"/>
       <c r="L225" s="1"/>
     </row>
-    <row r="226" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A226" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B226" s="5"/>
       <c r="D226" t="s">
-        <v>678</v>
-      </c>
-      <c r="E226" s="14" t="s">
-        <v>537</v>
+        <v>675</v>
+      </c>
+      <c r="E226" s="13" t="s">
+        <v>535</v>
       </c>
       <c r="F226" s="7" t="s">
         <v>149</v>
       </c>
       <c r="G226" s="7" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="H226" s="7" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="I226" s="7" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="J226" s="6" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="K226" s="5"/>
       <c r="L226" s="5"/>
     </row>
-    <row r="227" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A227" s="2" t="s">
         <v>105</v>
       </c>
@@ -7666,14 +7661,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="228" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
       <c r="D228" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E228" s="13"/>
+      <c r="E228" s="12"/>
       <c r="F228" s="1"/>
       <c r="G228" s="1"/>
       <c r="H228" s="1"/>
@@ -7682,43 +7677,43 @@
       <c r="K228" s="1"/>
       <c r="L228" s="1"/>
     </row>
-    <row r="229" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A229" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B229" s="5"/>
       <c r="D229" t="s">
+        <v>380</v>
+      </c>
+      <c r="E229" s="13" t="s">
+        <v>381</v>
+      </c>
+      <c r="F229" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G229" s="11" t="s">
         <v>382</v>
       </c>
-      <c r="E229" s="14" t="s">
+      <c r="H229" s="11" t="s">
         <v>383</v>
       </c>
-      <c r="F229" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="G229" s="12" t="s">
+      <c r="I229" s="11" t="s">
         <v>384</v>
       </c>
-      <c r="H229" s="12" t="s">
-        <v>385</v>
-      </c>
-      <c r="I229" s="12" t="s">
-        <v>386</v>
-      </c>
-      <c r="J229" s="18" t="s">
-        <v>376</v>
+      <c r="J229" s="17" t="s">
+        <v>374</v>
       </c>
       <c r="K229" s="5"/>
       <c r="L229" s="5"/>
     </row>
-    <row r="230" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A230" s="1"/>
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
-      <c r="D230" s="10" t="s">
+      <c r="D230" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="E230" s="13"/>
+      <c r="E230" s="12"/>
       <c r="F230" s="1"/>
       <c r="G230" s="1"/>
       <c r="H230" s="1"/>
@@ -7727,36 +7722,36 @@
       <c r="K230" s="1"/>
       <c r="L230" s="1"/>
     </row>
-    <row r="231" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A231" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B231" s="5"/>
-      <c r="D231" s="11" t="s">
+      <c r="D231" s="10" t="s">
+        <v>385</v>
+      </c>
+      <c r="E231" s="14" t="s">
+        <v>386</v>
+      </c>
+      <c r="F231" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="G231" s="11" t="s">
         <v>387</v>
       </c>
-      <c r="E231" s="15" t="s">
+      <c r="H231" s="11" t="s">
         <v>388</v>
       </c>
-      <c r="F231" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="G231" s="12" t="s">
+      <c r="I231" s="11" t="s">
         <v>389</v>
       </c>
-      <c r="H231" s="12" t="s">
-        <v>390</v>
-      </c>
-      <c r="I231" s="12" t="s">
-        <v>391</v>
-      </c>
-      <c r="J231" s="18" t="s">
-        <v>198</v>
+      <c r="J231" s="17" t="s">
+        <v>196</v>
       </c>
       <c r="K231" s="5"/>
       <c r="L231" s="5"/>
     </row>
-    <row r="232" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A232" s="2" t="s">
         <v>107</v>
       </c>
@@ -7776,14 +7771,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="233" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A233" s="1"/>
       <c r="B233" s="1"/>
       <c r="C233" s="1"/>
       <c r="D233" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E233" s="13"/>
+      <c r="E233" s="12"/>
       <c r="F233" s="1"/>
       <c r="G233" s="1"/>
       <c r="H233" s="1"/>
@@ -7792,43 +7787,43 @@
       <c r="K233" s="1"/>
       <c r="L233" s="1"/>
     </row>
-    <row r="234" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A234" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B234" s="5"/>
       <c r="D234" t="s">
+        <v>265</v>
+      </c>
+      <c r="E234" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="F234" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G234" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="H234" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="E234" s="14" t="s">
-        <v>247</v>
-      </c>
-      <c r="F234" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="G234" s="12" t="s">
+      <c r="I234" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="H234" s="12" t="s">
-        <v>269</v>
-      </c>
-      <c r="I234" s="12" t="s">
-        <v>270</v>
-      </c>
-      <c r="J234" s="18" t="s">
-        <v>198</v>
+      <c r="J234" s="17" t="s">
+        <v>196</v>
       </c>
       <c r="K234" s="5"/>
       <c r="L234" s="5"/>
     </row>
-    <row r="235" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A235" s="1"/>
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
       <c r="D235" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E235" s="13"/>
+      <c r="E235" s="12"/>
       <c r="F235" s="1"/>
       <c r="G235" s="1"/>
       <c r="H235" s="1"/>
@@ -7837,12 +7832,12 @@
       <c r="K235" s="1"/>
       <c r="L235" s="1"/>
     </row>
-    <row r="236" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A236" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B236" s="5"/>
-      <c r="E236" s="14"/>
+      <c r="E236" s="13"/>
       <c r="F236" s="5"/>
       <c r="G236" s="5"/>
       <c r="H236" s="5"/>
@@ -7851,7 +7846,7 @@
       <c r="K236" s="5"/>
       <c r="L236" s="5"/>
     </row>
-    <row r="237" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A237" s="2" t="s">
         <v>109</v>
       </c>
@@ -7871,14 +7866,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="238" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A238" s="1"/>
       <c r="B238" s="1"/>
       <c r="C238" s="1"/>
       <c r="D238" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E238" s="13"/>
+      <c r="E238" s="12"/>
       <c r="F238" s="1"/>
       <c r="G238" s="1"/>
       <c r="H238" s="1"/>
@@ -7887,43 +7882,43 @@
       <c r="K238" s="1"/>
       <c r="L238" s="1"/>
     </row>
-    <row r="239" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A239" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B239" s="5"/>
       <c r="D239" t="s">
-        <v>165</v>
-      </c>
-      <c r="E239" s="14" t="s">
-        <v>411</v>
-      </c>
-      <c r="F239" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="E239" s="13" t="s">
+        <v>409</v>
+      </c>
+      <c r="F239" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="G239" s="12" t="s">
+      <c r="G239" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="H239" s="12" t="s">
+      <c r="H239" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="I239" s="12" t="s">
+      <c r="I239" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="J239" s="18" t="s">
+      <c r="J239" s="17" t="s">
         <v>153</v>
       </c>
       <c r="K239" s="5"/>
       <c r="L239" s="5"/>
     </row>
-    <row r="240" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
       <c r="D240" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E240" s="13"/>
+      <c r="E240" s="12"/>
       <c r="F240" s="1"/>
       <c r="G240" s="1"/>
       <c r="H240" s="1"/>
@@ -7932,36 +7927,36 @@
       <c r="K240" s="1"/>
       <c r="L240" s="1"/>
     </row>
-    <row r="241" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A241" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B241" s="5"/>
       <c r="D241" t="s">
+        <v>445</v>
+      </c>
+      <c r="E241" s="13" t="s">
+        <v>446</v>
+      </c>
+      <c r="F241" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G241" s="11" t="s">
         <v>447</v>
       </c>
-      <c r="E241" s="14" t="s">
+      <c r="H241" s="11" t="s">
         <v>448</v>
       </c>
-      <c r="F241" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="G241" s="12" t="s">
+      <c r="I241" s="11" t="s">
         <v>449</v>
       </c>
-      <c r="H241" s="12" t="s">
-        <v>450</v>
-      </c>
-      <c r="I241" s="12" t="s">
-        <v>451</v>
-      </c>
-      <c r="J241" s="18" t="s">
-        <v>163</v>
+      <c r="J241" s="17" t="s">
+        <v>162</v>
       </c>
       <c r="K241" s="5"/>
       <c r="L241" s="5"/>
     </row>
-    <row r="242" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A242" s="2" t="s">
         <v>111</v>
       </c>
@@ -7981,14 +7976,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="243" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A243" s="1"/>
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
       <c r="D243" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E243" s="13"/>
+      <c r="E243" s="12"/>
       <c r="F243" s="1"/>
       <c r="G243" s="1"/>
       <c r="H243" s="1"/>
@@ -7997,43 +7992,43 @@
       <c r="K243" s="1"/>
       <c r="L243" s="1"/>
     </row>
-    <row r="244" spans="1:12" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A244" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B244" s="5"/>
       <c r="D244" t="s">
+        <v>525</v>
+      </c>
+      <c r="E244" s="13" t="s">
+        <v>364</v>
+      </c>
+      <c r="F244" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="G244" s="11" t="s">
+        <v>526</v>
+      </c>
+      <c r="H244" s="11" t="s">
         <v>527</v>
       </c>
-      <c r="E244" s="14" t="s">
-        <v>366</v>
-      </c>
-      <c r="F244" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="G244" s="12" t="s">
+      <c r="I244" s="11" t="s">
         <v>528</v>
       </c>
-      <c r="H244" s="12" t="s">
+      <c r="J244" s="21" t="s">
         <v>529</v>
-      </c>
-      <c r="I244" s="12" t="s">
-        <v>530</v>
-      </c>
-      <c r="J244" s="22" t="s">
-        <v>531</v>
       </c>
       <c r="K244" s="5"/>
       <c r="L244" s="5"/>
     </row>
-    <row r="245" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
       <c r="D245" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E245" s="13"/>
+      <c r="E245" s="12"/>
       <c r="F245" s="1"/>
       <c r="G245" s="1"/>
       <c r="H245" s="1"/>
@@ -8042,36 +8037,36 @@
       <c r="K245" s="1"/>
       <c r="L245" s="1"/>
     </row>
-    <row r="246" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A246" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B246" s="5"/>
       <c r="D246" t="s">
+        <v>558</v>
+      </c>
+      <c r="E246" s="13" t="s">
+        <v>554</v>
+      </c>
+      <c r="F246" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G246" s="11" t="s">
+        <v>559</v>
+      </c>
+      <c r="H246" s="11" t="s">
         <v>560</v>
       </c>
-      <c r="E246" s="14" t="s">
-        <v>556</v>
-      </c>
-      <c r="F246" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="G246" s="12" t="s">
+      <c r="I246" s="11" t="s">
         <v>561</v>
       </c>
-      <c r="H246" s="12" t="s">
-        <v>562</v>
-      </c>
-      <c r="I246" s="12" t="s">
-        <v>563</v>
-      </c>
-      <c r="J246" s="18" t="s">
-        <v>163</v>
+      <c r="J246" s="17" t="s">
+        <v>162</v>
       </c>
       <c r="K246" s="5"/>
       <c r="L246" s="5"/>
     </row>
-    <row r="247" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A247" s="2" t="s">
         <v>113</v>
       </c>
@@ -8091,14 +8086,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="248" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A248" s="1"/>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
       <c r="D248" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E248" s="13"/>
+      <c r="E248" s="12"/>
       <c r="F248" s="1"/>
       <c r="G248" s="1"/>
       <c r="H248" s="1"/>
@@ -8107,43 +8102,43 @@
       <c r="K248" s="1"/>
       <c r="L248" s="1"/>
     </row>
-    <row r="249" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A249" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B249" s="5"/>
       <c r="D249" t="s">
-        <v>188</v>
-      </c>
-      <c r="E249" s="14" t="s">
-        <v>189</v>
+        <v>186</v>
+      </c>
+      <c r="E249" s="13" t="s">
+        <v>187</v>
       </c>
       <c r="F249" s="7" t="s">
         <v>149</v>
       </c>
       <c r="G249" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="H249" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="I249" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="H249" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="I249" s="7" t="s">
-        <v>192</v>
-      </c>
       <c r="J249" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="K249" s="5"/>
       <c r="L249" s="5"/>
     </row>
-    <row r="250" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A250" s="1"/>
       <c r="B250" s="1"/>
       <c r="C250" s="1"/>
       <c r="D250" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E250" s="13"/>
+      <c r="E250" s="12"/>
       <c r="F250" s="1"/>
       <c r="G250" s="1"/>
       <c r="H250" s="1"/>
@@ -8152,36 +8147,36 @@
       <c r="K250" s="1"/>
       <c r="L250" s="1"/>
     </row>
-    <row r="251" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A251" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B251" s="5"/>
       <c r="D251" t="s">
+        <v>450</v>
+      </c>
+      <c r="E251" s="13" t="s">
+        <v>451</v>
+      </c>
+      <c r="F251" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="G251" s="11" t="s">
         <v>452</v>
       </c>
-      <c r="E251" s="14" t="s">
+      <c r="H251" s="11" t="s">
         <v>453</v>
       </c>
-      <c r="F251" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="G251" s="12" t="s">
+      <c r="I251" s="11" t="s">
         <v>454</v>
       </c>
-      <c r="H251" s="12" t="s">
-        <v>455</v>
-      </c>
-      <c r="I251" s="12" t="s">
-        <v>456</v>
-      </c>
-      <c r="J251" s="18" t="s">
-        <v>163</v>
+      <c r="J251" s="17" t="s">
+        <v>162</v>
       </c>
       <c r="K251" s="5"/>
       <c r="L251" s="5"/>
     </row>
-    <row r="252" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A252" s="2" t="s">
         <v>115</v>
       </c>
@@ -8201,14 +8196,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="253" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A253" s="1"/>
       <c r="B253" s="1"/>
       <c r="C253" s="1"/>
       <c r="D253" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E253" s="13"/>
+      <c r="E253" s="12"/>
       <c r="F253" s="1"/>
       <c r="G253" s="1"/>
       <c r="H253" s="1"/>
@@ -8217,43 +8212,43 @@
       <c r="K253" s="1"/>
       <c r="L253" s="1"/>
     </row>
-    <row r="254" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A254" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B254" s="5"/>
       <c r="D254" t="s">
+        <v>260</v>
+      </c>
+      <c r="E254" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="F254" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G254" s="11" t="s">
         <v>262</v>
       </c>
-      <c r="E254" s="14" t="s">
+      <c r="H254" s="11" t="s">
         <v>263</v>
       </c>
-      <c r="F254" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="G254" s="12" t="s">
+      <c r="I254" s="11" t="s">
         <v>264</v>
       </c>
-      <c r="H254" s="12" t="s">
-        <v>265</v>
-      </c>
-      <c r="I254" s="12" t="s">
-        <v>266</v>
-      </c>
-      <c r="J254" s="18" t="s">
-        <v>163</v>
+      <c r="J254" s="17" t="s">
+        <v>162</v>
       </c>
       <c r="K254" s="5"/>
       <c r="L254" s="5"/>
     </row>
-    <row r="255" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A255" s="1"/>
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
       <c r="D255" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E255" s="13"/>
+      <c r="E255" s="12"/>
       <c r="F255" s="1"/>
       <c r="G255" s="1"/>
       <c r="H255" s="1"/>
@@ -8262,36 +8257,36 @@
       <c r="K255" s="1"/>
       <c r="L255" s="1"/>
     </row>
-    <row r="256" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A256" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B256" s="5"/>
       <c r="D256" t="s">
+        <v>394</v>
+      </c>
+      <c r="E256" s="13" t="s">
+        <v>395</v>
+      </c>
+      <c r="F256" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G256" s="11" t="s">
         <v>396</v>
       </c>
-      <c r="E256" s="14" t="s">
+      <c r="H256" s="11" t="s">
         <v>397</v>
       </c>
-      <c r="F256" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="G256" s="12" t="s">
+      <c r="I256" s="11" t="s">
         <v>398</v>
       </c>
-      <c r="H256" s="12" t="s">
-        <v>399</v>
-      </c>
-      <c r="I256" s="12" t="s">
-        <v>400</v>
-      </c>
-      <c r="J256" s="18" t="s">
-        <v>158</v>
+      <c r="J256" s="17" t="s">
+        <v>157</v>
       </c>
       <c r="K256" s="5"/>
       <c r="L256" s="5"/>
     </row>
-    <row r="257" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A257" s="2" t="s">
         <v>117</v>
       </c>
@@ -8311,14 +8306,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="258" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
       <c r="D258" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E258" s="13"/>
+      <c r="E258" s="12"/>
       <c r="F258" s="1"/>
       <c r="G258" s="1"/>
       <c r="H258" s="1"/>
@@ -8327,43 +8322,43 @@
       <c r="K258" s="1"/>
       <c r="L258" s="1"/>
     </row>
-    <row r="259" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A259" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B259" s="5"/>
       <c r="D259" t="s">
+        <v>344</v>
+      </c>
+      <c r="E259" s="13" t="s">
+        <v>345</v>
+      </c>
+      <c r="F259" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G259" s="11" t="s">
         <v>346</v>
       </c>
-      <c r="E259" s="14" t="s">
+      <c r="H259" s="11" t="s">
         <v>347</v>
       </c>
-      <c r="F259" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="G259" s="12" t="s">
+      <c r="I259" s="11" t="s">
         <v>348</v>
       </c>
-      <c r="H259" s="12" t="s">
-        <v>349</v>
-      </c>
-      <c r="I259" s="12" t="s">
-        <v>350</v>
-      </c>
-      <c r="J259" s="18" t="s">
-        <v>198</v>
+      <c r="J259" s="17" t="s">
+        <v>196</v>
       </c>
       <c r="K259" s="5"/>
       <c r="L259" s="5"/>
     </row>
-    <row r="260" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A260" s="1"/>
       <c r="B260" s="1"/>
       <c r="C260" s="1"/>
       <c r="D260" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E260" s="13"/>
+      <c r="E260" s="12"/>
       <c r="F260" s="1"/>
       <c r="G260" s="1"/>
       <c r="H260" s="1"/>
@@ -8372,36 +8367,36 @@
       <c r="K260" s="1"/>
       <c r="L260" s="1"/>
     </row>
-    <row r="261" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A261" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B261" s="5"/>
       <c r="D261" t="s">
+        <v>431</v>
+      </c>
+      <c r="E261" s="13" t="s">
+        <v>432</v>
+      </c>
+      <c r="F261" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G261" s="11" t="s">
         <v>433</v>
       </c>
-      <c r="E261" s="14" t="s">
+      <c r="H261" s="11" t="s">
         <v>434</v>
       </c>
-      <c r="F261" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="G261" s="12" t="s">
+      <c r="I261" s="11" t="s">
         <v>435</v>
       </c>
-      <c r="H261" s="12" t="s">
-        <v>436</v>
-      </c>
-      <c r="I261" s="12" t="s">
-        <v>437</v>
-      </c>
-      <c r="J261" s="18" t="s">
-        <v>163</v>
+      <c r="J261" s="17" t="s">
+        <v>162</v>
       </c>
       <c r="K261" s="5"/>
       <c r="L261" s="5"/>
     </row>
-    <row r="262" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A262" s="2" t="s">
         <v>119</v>
       </c>
@@ -8421,14 +8416,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="263" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
       <c r="C263" s="1"/>
       <c r="D263" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E263" s="13"/>
+      <c r="E263" s="12"/>
       <c r="F263" s="1"/>
       <c r="G263" s="1"/>
       <c r="H263" s="1"/>
@@ -8437,43 +8432,43 @@
       <c r="K263" s="1"/>
       <c r="L263" s="1"/>
     </row>
-    <row r="264" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A264" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B264" s="5"/>
       <c r="D264" t="s">
+        <v>349</v>
+      </c>
+      <c r="E264" s="13" t="s">
+        <v>350</v>
+      </c>
+      <c r="F264" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G264" s="11" t="s">
         <v>351</v>
       </c>
-      <c r="E264" s="14" t="s">
+      <c r="H264" s="11" t="s">
         <v>352</v>
       </c>
-      <c r="F264" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="G264" s="12" t="s">
+      <c r="I264" s="11" t="s">
         <v>353</v>
       </c>
-      <c r="H264" s="12" t="s">
-        <v>354</v>
-      </c>
-      <c r="I264" s="12" t="s">
-        <v>355</v>
-      </c>
-      <c r="J264" s="18" t="s">
-        <v>198</v>
+      <c r="J264" s="17" t="s">
+        <v>196</v>
       </c>
       <c r="K264" s="5"/>
       <c r="L264" s="5"/>
     </row>
-    <row r="265" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A265" s="1"/>
       <c r="B265" s="1"/>
       <c r="C265" s="1"/>
       <c r="D265" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E265" s="13"/>
+      <c r="E265" s="12"/>
       <c r="F265" s="1"/>
       <c r="G265" s="1"/>
       <c r="H265" s="1"/>
@@ -8482,36 +8477,36 @@
       <c r="K265" s="1"/>
       <c r="L265" s="1"/>
     </row>
-    <row r="266" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A266" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B266" s="5"/>
       <c r="D266" t="s">
+        <v>455</v>
+      </c>
+      <c r="E266" s="13" t="s">
+        <v>456</v>
+      </c>
+      <c r="F266" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G266" s="11" t="s">
         <v>457</v>
       </c>
-      <c r="E266" s="14" t="s">
+      <c r="H266" s="11" t="s">
         <v>458</v>
       </c>
-      <c r="F266" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="G266" s="12" t="s">
+      <c r="I266" s="11" t="s">
         <v>459</v>
       </c>
-      <c r="H266" s="12" t="s">
+      <c r="J266" s="17" t="s">
         <v>460</v>
-      </c>
-      <c r="I266" s="12" t="s">
-        <v>461</v>
-      </c>
-      <c r="J266" s="18" t="s">
-        <v>462</v>
       </c>
       <c r="K266" s="5"/>
       <c r="L266" s="5"/>
     </row>
-    <row r="267" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A267" s="2" t="s">
         <v>121</v>
       </c>
@@ -8531,14 +8526,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="268" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A268" s="1"/>
       <c r="B268" s="1"/>
       <c r="C268" s="1"/>
       <c r="D268" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E268" s="13"/>
+      <c r="E268" s="12"/>
       <c r="F268" s="1"/>
       <c r="G268" s="1"/>
       <c r="H268" s="1"/>
@@ -8547,43 +8542,43 @@
       <c r="K268" s="1"/>
       <c r="L268" s="1"/>
     </row>
-    <row r="269" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A269" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B269" s="5"/>
       <c r="D269" t="s">
+        <v>375</v>
+      </c>
+      <c r="E269" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="F269" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="G269" s="11" t="s">
         <v>377</v>
       </c>
-      <c r="E269" s="14" t="s">
+      <c r="H269" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="F269" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="G269" s="12" t="s">
+      <c r="I269" s="11" t="s">
         <v>379</v>
       </c>
-      <c r="H269" s="12" t="s">
-        <v>380</v>
-      </c>
-      <c r="I269" s="12" t="s">
-        <v>381</v>
-      </c>
-      <c r="J269" s="18" t="s">
-        <v>376</v>
+      <c r="J269" s="17" t="s">
+        <v>374</v>
       </c>
       <c r="K269" s="5"/>
       <c r="L269" s="5"/>
     </row>
-    <row r="270" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A270" s="1"/>
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
       <c r="D270" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E270" s="13"/>
+      <c r="E270" s="12"/>
       <c r="F270" s="1"/>
       <c r="G270" s="1"/>
       <c r="H270" s="1"/>
@@ -8592,36 +8587,36 @@
       <c r="K270" s="1"/>
       <c r="L270" s="1"/>
     </row>
-    <row r="271" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A271" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B271" s="5"/>
       <c r="D271" t="s">
+        <v>499</v>
+      </c>
+      <c r="E271" s="13" t="s">
+        <v>381</v>
+      </c>
+      <c r="F271" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G271" s="11" t="s">
+        <v>500</v>
+      </c>
+      <c r="H271" s="11" t="s">
         <v>501</v>
       </c>
-      <c r="E271" s="14" t="s">
-        <v>383</v>
-      </c>
-      <c r="F271" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="G271" s="12" t="s">
-        <v>502</v>
-      </c>
-      <c r="H271" s="12" t="s">
-        <v>503</v>
-      </c>
-      <c r="I271" s="12" t="s">
-        <v>495</v>
-      </c>
-      <c r="J271" s="18" t="s">
+      <c r="I271" s="11" t="s">
+        <v>493</v>
+      </c>
+      <c r="J271" s="17" t="s">
         <v>153</v>
       </c>
       <c r="K271" s="5"/>
       <c r="L271" s="5"/>
     </row>
-    <row r="272" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A272" s="2" t="s">
         <v>123</v>
       </c>
@@ -8641,14 +8636,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="273" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A273" s="1"/>
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
       <c r="D273" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E273" s="13"/>
+      <c r="E273" s="12"/>
       <c r="F273" s="1"/>
       <c r="G273" s="1"/>
       <c r="H273" s="1"/>
@@ -8657,43 +8652,43 @@
       <c r="K273" s="1"/>
       <c r="L273" s="1"/>
     </row>
-    <row r="274" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A274" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B274" s="5"/>
       <c r="D274" t="s">
+        <v>399</v>
+      </c>
+      <c r="E274" s="13" t="s">
+        <v>400</v>
+      </c>
+      <c r="F274" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G274" s="11" t="s">
         <v>401</v>
       </c>
-      <c r="E274" s="14" t="s">
+      <c r="H274" s="11" t="s">
         <v>402</v>
       </c>
-      <c r="F274" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="G274" s="12" t="s">
+      <c r="I274" s="11" t="s">
         <v>403</v>
       </c>
-      <c r="H274" s="12" t="s">
-        <v>404</v>
-      </c>
-      <c r="I274" s="12" t="s">
-        <v>405</v>
-      </c>
-      <c r="J274" s="18" t="s">
-        <v>198</v>
+      <c r="J274" s="17" t="s">
+        <v>196</v>
       </c>
       <c r="K274" s="5"/>
       <c r="L274" s="5"/>
     </row>
-    <row r="275" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A275" s="1"/>
       <c r="B275" s="1"/>
       <c r="C275" s="1"/>
       <c r="D275" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E275" s="13"/>
+      <c r="E275" s="12"/>
       <c r="F275" s="1"/>
       <c r="G275" s="1"/>
       <c r="H275" s="1"/>
@@ -8702,36 +8697,36 @@
       <c r="K275" s="1"/>
       <c r="L275" s="1"/>
     </row>
-    <row r="276" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A276" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B276" s="5"/>
       <c r="D276" t="s">
-        <v>649</v>
-      </c>
-      <c r="E276" s="14" t="s">
-        <v>263</v>
+        <v>646</v>
+      </c>
+      <c r="E276" s="13" t="s">
+        <v>261</v>
       </c>
       <c r="F276" s="7" t="s">
         <v>149</v>
       </c>
       <c r="G276" s="7" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="H276" s="7" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="I276" s="7" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="J276" s="6" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="K276" s="5"/>
       <c r="L276" s="5"/>
     </row>
-    <row r="277" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A277" s="2" t="s">
         <v>125</v>
       </c>
@@ -8751,14 +8746,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="278" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A278" s="1"/>
       <c r="B278" s="1"/>
       <c r="C278" s="1"/>
       <c r="D278" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E278" s="13"/>
+      <c r="E278" s="12"/>
       <c r="F278" s="1"/>
       <c r="G278" s="1"/>
       <c r="H278" s="1"/>
@@ -8767,43 +8762,43 @@
       <c r="K278" s="1"/>
       <c r="L278" s="1"/>
     </row>
-    <row r="279" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A279" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B279" s="5"/>
       <c r="D279" t="s">
-        <v>220</v>
-      </c>
-      <c r="E279" s="14" t="s">
-        <v>221</v>
+        <v>218</v>
+      </c>
+      <c r="E279" s="13" t="s">
+        <v>219</v>
       </c>
       <c r="F279" s="7" t="s">
         <v>149</v>
       </c>
       <c r="G279" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="H279" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="I279" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="H279" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="I279" s="7" t="s">
-        <v>224</v>
-      </c>
       <c r="J279" s="6" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="K279" s="5"/>
       <c r="L279" s="5"/>
     </row>
-    <row r="280" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A280" s="1"/>
       <c r="B280" s="1"/>
       <c r="C280" s="1"/>
       <c r="D280" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E280" s="13"/>
+      <c r="E280" s="12"/>
       <c r="F280" s="1"/>
       <c r="G280" s="1"/>
       <c r="H280" s="1"/>
@@ -8812,28 +8807,28 @@
       <c r="K280" s="1"/>
       <c r="L280" s="1"/>
     </row>
-    <row r="281" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A281" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B281" s="5"/>
       <c r="D281" t="s">
-        <v>690</v>
-      </c>
-      <c r="E281" s="14" t="s">
-        <v>473</v>
+        <v>687</v>
+      </c>
+      <c r="E281" s="13" t="s">
+        <v>471</v>
       </c>
       <c r="F281" s="7" t="s">
         <v>149</v>
       </c>
       <c r="G281" s="7" t="s">
-        <v>691</v>
-      </c>
-      <c r="H281" s="8" t="s">
-        <v>716</v>
+        <v>688</v>
+      </c>
+      <c r="H281" s="7" t="s">
+        <v>713</v>
       </c>
       <c r="I281" s="7" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="J281" s="6" t="s">
         <v>153</v>
@@ -8841,7 +8836,7 @@
       <c r="K281" s="5"/>
       <c r="L281" s="5"/>
     </row>
-    <row r="282" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A282" s="2" t="s">
         <v>127</v>
       </c>
@@ -8861,14 +8856,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="283" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A283" s="1"/>
       <c r="B283" s="1"/>
       <c r="C283" s="1"/>
       <c r="D283" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E283" s="13"/>
+      <c r="E283" s="12"/>
       <c r="F283" s="1"/>
       <c r="G283" s="1"/>
       <c r="H283" s="1"/>
@@ -8877,43 +8872,43 @@
       <c r="K283" s="1"/>
       <c r="L283" s="1"/>
     </row>
-    <row r="284" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A284" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B284" s="5"/>
       <c r="D284" t="s">
+        <v>495</v>
+      </c>
+      <c r="E284" s="13" t="s">
+        <v>345</v>
+      </c>
+      <c r="F284" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G284" s="11" t="s">
+        <v>496</v>
+      </c>
+      <c r="H284" s="11" t="s">
         <v>497</v>
       </c>
-      <c r="E284" s="14" t="s">
-        <v>347</v>
-      </c>
-      <c r="F284" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="G284" s="12" t="s">
+      <c r="I284" s="11" t="s">
         <v>498</v>
       </c>
-      <c r="H284" s="12" t="s">
-        <v>499</v>
-      </c>
-      <c r="I284" s="12" t="s">
-        <v>500</v>
-      </c>
-      <c r="J284" s="18" t="s">
+      <c r="J284" s="17" t="s">
         <v>153</v>
       </c>
       <c r="K284" s="5"/>
       <c r="L284" s="5"/>
     </row>
-    <row r="285" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A285" s="1"/>
       <c r="B285" s="1"/>
       <c r="C285" s="1"/>
       <c r="D285" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E285" s="13"/>
+      <c r="E285" s="12"/>
       <c r="F285" s="1"/>
       <c r="G285" s="1"/>
       <c r="H285" s="1"/>
@@ -8922,36 +8917,36 @@
       <c r="K285" s="1"/>
       <c r="L285" s="1"/>
     </row>
-    <row r="286" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A286" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B286" s="5"/>
       <c r="D286" t="s">
+        <v>543</v>
+      </c>
+      <c r="E286" s="13" t="s">
+        <v>544</v>
+      </c>
+      <c r="F286" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G286" s="11" t="s">
         <v>545</v>
       </c>
-      <c r="E286" s="14" t="s">
+      <c r="H286" s="11" t="s">
         <v>546</v>
       </c>
-      <c r="F286" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="G286" s="12" t="s">
+      <c r="I286" s="11" t="s">
         <v>547</v>
       </c>
-      <c r="H286" s="12" t="s">
-        <v>548</v>
-      </c>
-      <c r="I286" s="12" t="s">
-        <v>549</v>
-      </c>
-      <c r="J286" s="18" t="s">
-        <v>370</v>
+      <c r="J286" s="17" t="s">
+        <v>368</v>
       </c>
       <c r="K286" s="5"/>
       <c r="L286" s="5"/>
     </row>
-    <row r="287" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A287" s="2" t="s">
         <v>129</v>
       </c>
@@ -8971,14 +8966,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="288" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A288" s="1"/>
       <c r="B288" s="1"/>
       <c r="C288" s="1"/>
       <c r="D288" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E288" s="13"/>
+      <c r="E288" s="12"/>
       <c r="F288" s="1"/>
       <c r="G288" s="1"/>
       <c r="H288" s="1"/>
@@ -8987,43 +8982,43 @@
       <c r="K288" s="1"/>
       <c r="L288" s="1"/>
     </row>
-    <row r="289" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A289" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B289" s="5"/>
       <c r="D289" t="s">
+        <v>363</v>
+      </c>
+      <c r="E289" s="13" t="s">
+        <v>364</v>
+      </c>
+      <c r="F289" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="G289" s="11" t="s">
         <v>365</v>
       </c>
-      <c r="E289" s="14" t="s">
+      <c r="H289" s="11" t="s">
         <v>366</v>
       </c>
-      <c r="F289" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="G289" s="12" t="s">
+      <c r="I289" s="11" t="s">
         <v>367</v>
       </c>
-      <c r="H289" s="12" t="s">
+      <c r="J289" s="17" t="s">
         <v>368</v>
-      </c>
-      <c r="I289" s="12" t="s">
-        <v>369</v>
-      </c>
-      <c r="J289" s="18" t="s">
-        <v>370</v>
       </c>
       <c r="K289" s="5"/>
       <c r="L289" s="5"/>
     </row>
-    <row r="290" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A290" s="1"/>
       <c r="B290" s="1"/>
       <c r="C290" s="1"/>
       <c r="D290" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E290" s="13"/>
+      <c r="E290" s="12"/>
       <c r="F290" s="1"/>
       <c r="G290" s="1"/>
       <c r="H290" s="1"/>
@@ -9032,36 +9027,36 @@
       <c r="K290" s="1"/>
       <c r="L290" s="1"/>
     </row>
-    <row r="291" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A291" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B291" s="5"/>
       <c r="D291" t="s">
+        <v>548</v>
+      </c>
+      <c r="E291" s="13" t="s">
+        <v>549</v>
+      </c>
+      <c r="F291" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="G291" s="11" t="s">
         <v>550</v>
       </c>
-      <c r="E291" s="14" t="s">
+      <c r="H291" s="11" t="s">
         <v>551</v>
       </c>
-      <c r="F291" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="G291" s="12" t="s">
+      <c r="I291" s="11" t="s">
         <v>552</v>
       </c>
-      <c r="H291" s="12" t="s">
-        <v>553</v>
-      </c>
-      <c r="I291" s="12" t="s">
-        <v>554</v>
-      </c>
-      <c r="J291" s="18" t="s">
-        <v>163</v>
+      <c r="J291" s="17" t="s">
+        <v>162</v>
       </c>
       <c r="K291" s="5"/>
       <c r="L291" s="5"/>
     </row>
-    <row r="292" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A292" s="2" t="s">
         <v>131</v>
       </c>
@@ -9081,14 +9076,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="293" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A293" s="1"/>
       <c r="B293" s="1"/>
       <c r="C293" s="1"/>
       <c r="D293" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E293" s="13"/>
+      <c r="E293" s="12"/>
       <c r="F293" s="1"/>
       <c r="G293" s="1"/>
       <c r="H293" s="1"/>
@@ -9097,43 +9092,43 @@
       <c r="K293" s="1"/>
       <c r="L293" s="1"/>
     </row>
-    <row r="294" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A294" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B294" s="5"/>
       <c r="D294" t="s">
+        <v>310</v>
+      </c>
+      <c r="E294" s="13" t="s">
+        <v>311</v>
+      </c>
+      <c r="F294" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="G294" s="11" t="s">
         <v>312</v>
       </c>
-      <c r="E294" s="14" t="s">
+      <c r="H294" s="11" t="s">
         <v>313</v>
       </c>
-      <c r="F294" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="G294" s="12" t="s">
+      <c r="I294" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="H294" s="12" t="s">
-        <v>315</v>
-      </c>
-      <c r="I294" s="12" t="s">
-        <v>316</v>
-      </c>
-      <c r="J294" s="18" t="s">
-        <v>158</v>
+      <c r="J294" s="17" t="s">
+        <v>157</v>
       </c>
       <c r="K294" s="5"/>
       <c r="L294" s="5"/>
     </row>
-    <row r="295" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A295" s="1"/>
       <c r="B295" s="1"/>
       <c r="C295" s="1"/>
       <c r="D295" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E295" s="13"/>
+      <c r="E295" s="12"/>
       <c r="F295" s="1"/>
       <c r="G295" s="1"/>
       <c r="H295" s="1"/>
@@ -9142,36 +9137,36 @@
       <c r="K295" s="1"/>
       <c r="L295" s="1"/>
     </row>
-    <row r="296" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A296" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B296" s="5"/>
       <c r="D296" t="s">
+        <v>505</v>
+      </c>
+      <c r="E296" s="13" t="s">
+        <v>506</v>
+      </c>
+      <c r="F296" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="G296" s="11" t="s">
         <v>507</v>
       </c>
-      <c r="E296" s="14" t="s">
+      <c r="H296" s="11" t="s">
         <v>508</v>
       </c>
-      <c r="F296" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="G296" s="12" t="s">
+      <c r="I296" s="11" t="s">
         <v>509</v>
       </c>
-      <c r="H296" s="12" t="s">
-        <v>510</v>
-      </c>
-      <c r="I296" s="12" t="s">
-        <v>511</v>
-      </c>
-      <c r="J296" s="18" t="s">
-        <v>376</v>
+      <c r="J296" s="17" t="s">
+        <v>374</v>
       </c>
       <c r="K296" s="5"/>
       <c r="L296" s="5"/>
     </row>
-    <row r="297" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A297" s="2" t="s">
         <v>133</v>
       </c>
@@ -9191,14 +9186,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="298" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A298" s="1"/>
       <c r="B298" s="1"/>
       <c r="C298" s="1"/>
       <c r="D298" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E298" s="13"/>
+      <c r="E298" s="12"/>
       <c r="F298" s="1"/>
       <c r="G298" s="1"/>
       <c r="H298" s="1"/>
@@ -9207,43 +9202,43 @@
       <c r="K298" s="1"/>
       <c r="L298" s="1"/>
     </row>
-    <row r="299" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A299" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B299" s="5"/>
       <c r="D299" t="s">
-        <v>215</v>
-      </c>
-      <c r="E299" s="14" t="s">
-        <v>216</v>
+        <v>213</v>
+      </c>
+      <c r="E299" s="13" t="s">
+        <v>214</v>
       </c>
       <c r="F299" s="7" t="s">
         <v>149</v>
       </c>
       <c r="G299" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="H299" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="I299" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="H299" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="I299" s="7" t="s">
-        <v>219</v>
-      </c>
       <c r="J299" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K299" s="5"/>
       <c r="L299" s="5"/>
     </row>
-    <row r="300" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A300" s="1"/>
       <c r="B300" s="1"/>
       <c r="C300" s="1"/>
       <c r="D300" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E300" s="13"/>
+      <c r="E300" s="12"/>
       <c r="F300" s="1"/>
       <c r="G300" s="1"/>
       <c r="H300" s="1"/>
@@ -9252,36 +9247,36 @@
       <c r="K300" s="1"/>
       <c r="L300" s="1"/>
     </row>
-    <row r="301" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:12" ht="24" x14ac:dyDescent="0.2">
       <c r="A301" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B301" s="5"/>
       <c r="D301" t="s">
+        <v>440</v>
+      </c>
+      <c r="E301" s="20" t="s">
+        <v>441</v>
+      </c>
+      <c r="F301" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="G301" s="11" t="s">
         <v>442</v>
       </c>
-      <c r="E301" s="21" t="s">
+      <c r="H301" s="11" t="s">
         <v>443</v>
       </c>
-      <c r="F301" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="G301" s="12" t="s">
+      <c r="I301" s="11" t="s">
         <v>444</v>
       </c>
-      <c r="H301" s="12" t="s">
-        <v>445</v>
-      </c>
-      <c r="I301" s="12" t="s">
-        <v>446</v>
-      </c>
-      <c r="J301" s="18" t="s">
-        <v>198</v>
+      <c r="J301" s="17" t="s">
+        <v>196</v>
       </c>
       <c r="K301" s="5"/>
       <c r="L301" s="5"/>
     </row>
-    <row r="302" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A302" s="2" t="s">
         <v>135</v>
       </c>
@@ -9301,14 +9296,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="303" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A303" s="1"/>
       <c r="B303" s="1"/>
       <c r="C303" s="1"/>
       <c r="D303" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E303" s="13"/>
+      <c r="E303" s="12"/>
       <c r="F303" s="1"/>
       <c r="G303" s="1"/>
       <c r="H303" s="1"/>
@@ -9317,43 +9312,43 @@
       <c r="K303" s="1"/>
       <c r="L303" s="1"/>
     </row>
-    <row r="304" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A304" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B304" s="5"/>
       <c r="D304" t="s">
-        <v>173</v>
-      </c>
-      <c r="E304" s="14" t="s">
-        <v>183</v>
+        <v>172</v>
+      </c>
+      <c r="E304" s="13" t="s">
+        <v>181</v>
       </c>
       <c r="F304" s="7" t="s">
         <v>149</v>
       </c>
       <c r="G304" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="H304" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="H304" s="7" t="s">
+      <c r="I304" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="I304" s="7" t="s">
-        <v>176</v>
-      </c>
       <c r="J304" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="K304" s="5"/>
       <c r="L304" s="5"/>
     </row>
-    <row r="305" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A305" s="1"/>
       <c r="B305" s="1"/>
       <c r="C305" s="1"/>
       <c r="D305" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E305" s="13"/>
+      <c r="E305" s="12"/>
       <c r="F305" s="1"/>
       <c r="G305" s="1"/>
       <c r="H305" s="1"/>
@@ -9362,36 +9357,36 @@
       <c r="K305" s="1"/>
       <c r="L305" s="1"/>
     </row>
-    <row r="306" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A306" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B306" s="5"/>
       <c r="D306" t="s">
+        <v>461</v>
+      </c>
+      <c r="E306" s="13" t="s">
+        <v>381</v>
+      </c>
+      <c r="F306" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G306" s="11" t="s">
+        <v>462</v>
+      </c>
+      <c r="H306" s="11" t="s">
         <v>463</v>
       </c>
-      <c r="E306" s="14" t="s">
-        <v>383</v>
-      </c>
-      <c r="F306" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="G306" s="12" t="s">
+      <c r="I306" s="11" t="s">
         <v>464</v>
       </c>
-      <c r="H306" s="12" t="s">
-        <v>465</v>
-      </c>
-      <c r="I306" s="12" t="s">
-        <v>466</v>
-      </c>
-      <c r="J306" s="18" t="s">
-        <v>163</v>
+      <c r="J306" s="17" t="s">
+        <v>162</v>
       </c>
       <c r="K306" s="5"/>
       <c r="L306" s="5"/>
     </row>
-    <row r="307" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A307" s="2" t="s">
         <v>137</v>
       </c>
@@ -9411,14 +9406,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="308" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A308" s="1"/>
       <c r="B308" s="1"/>
       <c r="C308" s="1"/>
       <c r="D308" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E308" s="13"/>
+      <c r="E308" s="12"/>
       <c r="F308" s="1"/>
       <c r="G308" s="1"/>
       <c r="H308" s="1"/>
@@ -9427,43 +9422,43 @@
       <c r="K308" s="1"/>
       <c r="L308" s="1"/>
     </row>
-    <row r="309" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A309" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B309" s="5"/>
       <c r="D309" t="s">
+        <v>335</v>
+      </c>
+      <c r="E309" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="F309" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G309" s="11" t="s">
+        <v>336</v>
+      </c>
+      <c r="H309" s="11" t="s">
         <v>337</v>
       </c>
-      <c r="E309" s="14" t="s">
-        <v>183</v>
-      </c>
-      <c r="F309" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="G309" s="12" t="s">
+      <c r="I309" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="H309" s="12" t="s">
-        <v>339</v>
-      </c>
-      <c r="I309" s="12" t="s">
-        <v>340</v>
-      </c>
-      <c r="J309" s="18" t="s">
-        <v>198</v>
+      <c r="J309" s="17" t="s">
+        <v>196</v>
       </c>
       <c r="K309" s="5"/>
       <c r="L309" s="5"/>
     </row>
-    <row r="310" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A310" s="1"/>
       <c r="B310" s="1"/>
       <c r="C310" s="1"/>
       <c r="D310" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E310" s="13"/>
+      <c r="E310" s="12"/>
       <c r="F310" s="1"/>
       <c r="G310" s="1"/>
       <c r="H310" s="1"/>
@@ -9472,36 +9467,36 @@
       <c r="K310" s="1"/>
       <c r="L310" s="1"/>
     </row>
-    <row r="311" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A311" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B311" s="5"/>
       <c r="D311" t="s">
+        <v>530</v>
+      </c>
+      <c r="E311" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="F311" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G311" s="11" t="s">
+        <v>531</v>
+      </c>
+      <c r="H311" s="11" t="s">
         <v>532</v>
       </c>
-      <c r="E311" s="14" t="s">
-        <v>183</v>
-      </c>
-      <c r="F311" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="G311" s="12" t="s">
+      <c r="I311" s="11" t="s">
         <v>533</v>
       </c>
-      <c r="H311" s="12" t="s">
-        <v>534</v>
-      </c>
-      <c r="I311" s="12" t="s">
-        <v>535</v>
-      </c>
-      <c r="J311" s="18" t="s">
-        <v>163</v>
+      <c r="J311" s="17" t="s">
+        <v>162</v>
       </c>
       <c r="K311" s="5"/>
       <c r="L311" s="5"/>
     </row>
-    <row r="312" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A312" s="2" t="s">
         <v>139</v>
       </c>
@@ -9521,14 +9516,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="313" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A313" s="1"/>
       <c r="B313" s="1"/>
       <c r="C313" s="1"/>
       <c r="D313" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E313" s="13"/>
+      <c r="E313" s="12"/>
       <c r="F313" s="1"/>
       <c r="G313" s="1"/>
       <c r="H313" s="1"/>
@@ -9537,43 +9532,43 @@
       <c r="K313" s="1"/>
       <c r="L313" s="1"/>
     </row>
-    <row r="314" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A314" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B314" s="5"/>
       <c r="D314" t="s">
-        <v>204</v>
-      </c>
-      <c r="E314" s="14" t="s">
-        <v>205</v>
+        <v>202</v>
+      </c>
+      <c r="E314" s="13" t="s">
+        <v>203</v>
       </c>
       <c r="F314" s="7" t="s">
         <v>149</v>
       </c>
       <c r="G314" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="H314" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="I314" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="H314" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="I314" s="7" t="s">
-        <v>208</v>
-      </c>
       <c r="J314" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="K314" s="5"/>
       <c r="L314" s="5"/>
     </row>
-    <row r="315" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A315" s="1"/>
       <c r="B315" s="1"/>
       <c r="C315" s="1"/>
       <c r="D315" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E315" s="13"/>
+      <c r="E315" s="12"/>
       <c r="F315" s="1"/>
       <c r="G315" s="1"/>
       <c r="H315" s="1"/>
@@ -9582,36 +9577,36 @@
       <c r="K315" s="1"/>
       <c r="L315" s="1"/>
     </row>
-    <row r="316" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A316" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B316" s="5"/>
       <c r="D316" t="s">
+        <v>475</v>
+      </c>
+      <c r="E316" s="13" t="s">
+        <v>476</v>
+      </c>
+      <c r="F316" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="G316" s="11" t="s">
         <v>477</v>
       </c>
-      <c r="E316" s="14" t="s">
+      <c r="H316" s="11" t="s">
         <v>478</v>
       </c>
-      <c r="F316" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="G316" s="12" t="s">
+      <c r="I316" s="11" t="s">
         <v>479</v>
       </c>
-      <c r="H316" s="12" t="s">
-        <v>480</v>
-      </c>
-      <c r="I316" s="12" t="s">
-        <v>481</v>
-      </c>
-      <c r="J316" s="18" t="s">
-        <v>163</v>
+      <c r="J316" s="17" t="s">
+        <v>162</v>
       </c>
       <c r="K316" s="5"/>
       <c r="L316" s="5"/>
     </row>
-    <row r="317" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A317" s="2" t="s">
         <v>141</v>
       </c>
@@ -9631,14 +9626,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="318" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A318" s="1"/>
       <c r="B318" s="1"/>
       <c r="C318" s="1"/>
       <c r="D318" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E318" s="13"/>
+      <c r="E318" s="12"/>
       <c r="F318" s="1"/>
       <c r="G318" s="1"/>
       <c r="H318" s="1"/>
@@ -9647,43 +9642,43 @@
       <c r="K318" s="1"/>
       <c r="L318" s="1"/>
     </row>
-    <row r="319" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A319" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B319" s="5"/>
       <c r="D319" t="s">
-        <v>235</v>
-      </c>
-      <c r="E319" s="14" t="s">
-        <v>236</v>
+        <v>233</v>
+      </c>
+      <c r="E319" s="13" t="s">
+        <v>234</v>
       </c>
       <c r="F319" s="7" t="s">
         <v>149</v>
       </c>
       <c r="G319" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="H319" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="I319" s="7" t="s">
         <v>237</v>
       </c>
-      <c r="H319" s="7" t="s">
+      <c r="J319" s="6" t="s">
         <v>238</v>
-      </c>
-      <c r="I319" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="J319" s="6" t="s">
-        <v>240</v>
       </c>
       <c r="K319" s="5"/>
       <c r="L319" s="5"/>
     </row>
-    <row r="320" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A320" s="1"/>
       <c r="B320" s="1"/>
-      <c r="C320" s="10"/>
-      <c r="D320" s="10" t="s">
+      <c r="C320" s="9"/>
+      <c r="D320" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="E320" s="13"/>
+      <c r="E320" s="12"/>
       <c r="F320" s="1"/>
       <c r="G320" s="1"/>
       <c r="H320" s="1"/>
@@ -9692,119 +9687,119 @@
       <c r="K320" s="1"/>
       <c r="L320" s="1"/>
     </row>
-    <row r="321" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A321" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B321" s="9"/>
-      <c r="C321" s="11"/>
-      <c r="D321" s="11" t="s">
-        <v>621</v>
-      </c>
-      <c r="E321" s="15" t="s">
-        <v>183</v>
+      <c r="B321" s="8"/>
+      <c r="C321" s="10"/>
+      <c r="D321" s="10" t="s">
+        <v>618</v>
+      </c>
+      <c r="E321" s="14" t="s">
+        <v>181</v>
       </c>
       <c r="F321" s="7" t="s">
         <v>149</v>
       </c>
       <c r="G321" s="7" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="H321" s="7" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="I321" s="7" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="J321" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="K321" s="5"/>
       <c r="L321" s="5"/>
     </row>
-    <row r="323" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="H323" s="27" t="s">
+    <row r="323" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H323" s="23" t="s">
         <v>143</v>
       </c>
-      <c r="I323" s="28"/>
-    </row>
-    <row r="325" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="H325" s="27" t="s">
+      <c r="I323" s="24"/>
+    </row>
+    <row r="325" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H325" s="23" t="s">
         <v>144</v>
       </c>
-      <c r="I325" s="28"/>
+      <c r="I325" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="66">
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="D22:H22"/>
+    <mergeCell ref="D27:H27"/>
+    <mergeCell ref="D32:H32"/>
+    <mergeCell ref="D37:H37"/>
+    <mergeCell ref="D42:H42"/>
+    <mergeCell ref="D47:H47"/>
+    <mergeCell ref="D52:H52"/>
+    <mergeCell ref="D57:H57"/>
+    <mergeCell ref="D62:H62"/>
+    <mergeCell ref="D67:H67"/>
+    <mergeCell ref="D72:H72"/>
+    <mergeCell ref="D77:H77"/>
+    <mergeCell ref="D82:H82"/>
+    <mergeCell ref="D87:H87"/>
+    <mergeCell ref="D92:H92"/>
+    <mergeCell ref="D97:H97"/>
+    <mergeCell ref="D102:H102"/>
+    <mergeCell ref="D107:H107"/>
+    <mergeCell ref="D112:H112"/>
+    <mergeCell ref="D117:H117"/>
+    <mergeCell ref="D122:H122"/>
+    <mergeCell ref="D127:H127"/>
+    <mergeCell ref="D132:H132"/>
+    <mergeCell ref="D137:H137"/>
+    <mergeCell ref="D142:H142"/>
+    <mergeCell ref="D147:H147"/>
+    <mergeCell ref="D152:H152"/>
+    <mergeCell ref="D157:H157"/>
+    <mergeCell ref="D162:H162"/>
+    <mergeCell ref="D167:H167"/>
+    <mergeCell ref="D172:H172"/>
+    <mergeCell ref="D177:H177"/>
+    <mergeCell ref="D182:H182"/>
+    <mergeCell ref="D187:H187"/>
+    <mergeCell ref="D192:H192"/>
+    <mergeCell ref="D197:H197"/>
+    <mergeCell ref="D202:H202"/>
+    <mergeCell ref="D207:H207"/>
+    <mergeCell ref="D212:H212"/>
+    <mergeCell ref="D217:H217"/>
+    <mergeCell ref="D222:H222"/>
+    <mergeCell ref="D227:H227"/>
+    <mergeCell ref="D232:H232"/>
+    <mergeCell ref="D237:H237"/>
+    <mergeCell ref="D242:H242"/>
+    <mergeCell ref="D247:H247"/>
+    <mergeCell ref="D252:H252"/>
+    <mergeCell ref="D257:H257"/>
+    <mergeCell ref="D262:H262"/>
+    <mergeCell ref="D267:H267"/>
+    <mergeCell ref="D272:H272"/>
+    <mergeCell ref="D277:H277"/>
+    <mergeCell ref="D282:H282"/>
+    <mergeCell ref="D287:H287"/>
+    <mergeCell ref="D292:H292"/>
+    <mergeCell ref="D297:H297"/>
     <mergeCell ref="H325:I325"/>
     <mergeCell ref="D302:H302"/>
     <mergeCell ref="D307:H307"/>
     <mergeCell ref="D312:H312"/>
     <mergeCell ref="D317:H317"/>
     <mergeCell ref="H323:I323"/>
-    <mergeCell ref="D277:H277"/>
-    <mergeCell ref="D282:H282"/>
-    <mergeCell ref="D287:H287"/>
-    <mergeCell ref="D292:H292"/>
-    <mergeCell ref="D297:H297"/>
-    <mergeCell ref="D252:H252"/>
-    <mergeCell ref="D257:H257"/>
-    <mergeCell ref="D262:H262"/>
-    <mergeCell ref="D267:H267"/>
-    <mergeCell ref="D272:H272"/>
-    <mergeCell ref="D227:H227"/>
-    <mergeCell ref="D232:H232"/>
-    <mergeCell ref="D237:H237"/>
-    <mergeCell ref="D242:H242"/>
-    <mergeCell ref="D247:H247"/>
-    <mergeCell ref="D202:H202"/>
-    <mergeCell ref="D207:H207"/>
-    <mergeCell ref="D212:H212"/>
-    <mergeCell ref="D217:H217"/>
-    <mergeCell ref="D222:H222"/>
-    <mergeCell ref="D177:H177"/>
-    <mergeCell ref="D182:H182"/>
-    <mergeCell ref="D187:H187"/>
-    <mergeCell ref="D192:H192"/>
-    <mergeCell ref="D197:H197"/>
-    <mergeCell ref="D152:H152"/>
-    <mergeCell ref="D157:H157"/>
-    <mergeCell ref="D162:H162"/>
-    <mergeCell ref="D167:H167"/>
-    <mergeCell ref="D172:H172"/>
-    <mergeCell ref="D127:H127"/>
-    <mergeCell ref="D132:H132"/>
-    <mergeCell ref="D137:H137"/>
-    <mergeCell ref="D142:H142"/>
-    <mergeCell ref="D147:H147"/>
-    <mergeCell ref="D102:H102"/>
-    <mergeCell ref="D107:H107"/>
-    <mergeCell ref="D112:H112"/>
-    <mergeCell ref="D117:H117"/>
-    <mergeCell ref="D122:H122"/>
-    <mergeCell ref="D77:H77"/>
-    <mergeCell ref="D82:H82"/>
-    <mergeCell ref="D87:H87"/>
-    <mergeCell ref="D92:H92"/>
-    <mergeCell ref="D97:H97"/>
-    <mergeCell ref="D52:H52"/>
-    <mergeCell ref="D57:H57"/>
-    <mergeCell ref="D62:H62"/>
-    <mergeCell ref="D67:H67"/>
-    <mergeCell ref="D72:H72"/>
-    <mergeCell ref="D27:H27"/>
-    <mergeCell ref="D32:H32"/>
-    <mergeCell ref="D37:H37"/>
-    <mergeCell ref="D42:H42"/>
-    <mergeCell ref="D47:H47"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="D22:H22"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="B4 B321 B319 B316 B314 B311 B309 B306 B304 B301 B299 B296 B294 B291 B289 B286 B284 B281 B279 B276 B274 B271 B269 B266 B264 B261 B259 B256 B254 B251 B249 B246 B244 B241 B239 B236 B234 B231 B229 B226 B224 B221 B219 B216 B214 B211 B209 B206 B204 B201 B199 B196 B194 B191 B189 B186 B184 B181 B179 B176 B174 B171 B169 B166 B164 B161 B159 B156 B154 B151 B149 B146 B144 B141 B139 B136 B134 B131 B129 B126 B124 B121 B119 B116 B114 B111 B109 B106 B104 B101 B99 B96 B94 B91 B89 B86 B84 B81 B79 B76 B74 B71 B69 B66 B64 B61 B59 B56 B54 B51 B49 B46 B44 B41 B39 B36 B34 B31 B29 B26 B24 B21 B19 B16 B14 B11 B9 B6">
+    <dataValidation type="list" allowBlank="1" sqref="B4 B321 B319 B316 B314 B311 B309 B306 B304 B301 B299 B296 B294 B291 B289 B286 B284 B281 B279 B276 B274 B271 B269 B266 B264 B261 B259 B256 B254 B251 B249 B246 B244 B241 B239 B236 B234 B231 B229 B226 B224 B221 B219 B216 B214 B211 B209 B206 B204 B201 B199 B196 B194 B191 B189 B186 B184 B181 B179 B176 B174 B171 B169 B166 B164 B161 B159 B156 B154 B151 B149 B146 B144 B141 B139 B136 B134 B131 B129 B126 B124 B121 B119 B116 B114 B111 B109 B106 B104 B101 B99 B96 B94 B91 B89 B86 B84 B81 B79 B76 B74 B71 B69 B66 B64 B61 B59 B56 B54 B51 B49 B46 B44 B41 B39 B36 B34 B31 B29 B26 B24 B21 B19 B16 B14 B11 B9 B6" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"ДА,НЕ"</formula1>
     </dataValidation>
   </dataValidations>
